--- a/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
+++ b/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/cpaltat_upv_edu_es/Documents/TFM/Data/Annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1203" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35E5BBAE-D9EC-4529-8AF5-9405C0A6DBD8}"/>
+  <xr:revisionPtr revIDLastSave="1205" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55559726-6660-4544-981E-7684B9026A1A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5100" yWindow="855" windowWidth="14850" windowHeight="9307" xr2:uid="{49184B03-C425-4292-8179-3E0C1E060977}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{49184B03-C425-4292-8179-3E0C1E060977}"/>
   </bookViews>
   <sheets>
     <sheet name="Argument annotations" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>Page</t>
   </si>
   <si>
-    <t>File</t>
-  </si>
-  <si>
     <t>Argument</t>
   </si>
   <si>
@@ -190,9 +187,6 @@
   </si>
   <si>
     <t>ODS (0-17)</t>
-  </si>
-  <si>
-    <t>S (Apoyo)/ A (Ataque)</t>
   </si>
   <si>
     <t>From 2015 to 2019, the world 
@@ -2186,6 +2180,12 @@
   </si>
   <si>
     <t>GLOBAL_SGD2023_</t>
+  </si>
+  <si>
+    <t>Prefix</t>
+  </si>
+  <si>
+    <t>RelWithODS</t>
   </si>
 </sst>
 </file>
@@ -2774,24 +2774,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>452</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -2800,15 +2800,15 @@
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -2817,32 +2817,32 @@
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -2851,15 +2851,15 @@
         <v>0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -2868,15 +2868,15 @@
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -2885,49 +2885,49 @@
         <v>0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B8">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B10">
         <v>7</v>
@@ -2936,32 +2936,32 @@
         <v>16</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B12">
         <v>7</v>
@@ -2970,49 +2970,49 @@
         <v>17</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -3021,15 +3021,15 @@
         <v>4</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -3038,49 +3038,49 @@
         <v>4</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B17">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B18">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B19">
         <v>13</v>
@@ -3089,66 +3089,66 @@
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B20">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B21">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B22">
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B23">
         <v>13</v>
@@ -3157,49 +3157,49 @@
         <v>10</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B24">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B25">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B26">
         <v>13</v>
@@ -3208,32 +3208,32 @@
         <v>17</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B27">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B28">
         <v>14</v>
@@ -3242,15 +3242,15 @@
         <v>3</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B29">
         <v>14</v>
@@ -3259,15 +3259,15 @@
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B30">
         <v>14</v>
@@ -3276,15 +3276,15 @@
         <v>11.12</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B31">
         <v>14</v>
@@ -3293,15 +3293,15 @@
         <v>11</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B32">
         <v>14</v>
@@ -3310,15 +3310,15 @@
         <v>9</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B33">
         <v>15</v>
@@ -3327,32 +3327,32 @@
         <v>16</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B34">
         <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B35">
         <v>15</v>
@@ -3361,15 +3361,15 @@
         <v>16</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B36">
         <v>15</v>
@@ -3378,15 +3378,15 @@
         <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B37">
         <v>15</v>
@@ -3395,15 +3395,15 @@
         <v>10</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B38">
         <v>15</v>
@@ -3412,15 +3412,15 @@
         <v>5</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B39">
         <v>15</v>
@@ -3429,57 +3429,57 @@
         <v>0</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B40">
         <v>15</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B41">
         <v>15</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B42">
         <v>15</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B43">
         <v>16</v>
@@ -3488,15 +3488,15 @@
         <v>15</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B44">
         <v>16</v>
@@ -3505,15 +3505,15 @@
         <v>15</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B45">
         <v>16</v>
@@ -3522,49 +3522,49 @@
         <v>6</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E45" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B46">
         <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B47">
         <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B48">
         <v>16</v>
@@ -3573,15 +3573,15 @@
         <v>14</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B49">
         <v>17</v>
@@ -3590,15 +3590,15 @@
         <v>14</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B50">
         <v>17</v>
@@ -3607,15 +3607,15 @@
         <v>14</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B51">
         <v>17</v>
@@ -3624,15 +3624,15 @@
         <v>14</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E51" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B52">
         <v>17</v>
@@ -3641,15 +3641,15 @@
         <v>14</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B53">
         <v>17</v>
@@ -3658,15 +3658,15 @@
         <v>14</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E53" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B54">
         <v>17</v>
@@ -3675,15 +3675,15 @@
         <v>14</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B55">
         <v>17</v>
@@ -3692,15 +3692,15 @@
         <v>14</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B56">
         <v>17</v>
@@ -3709,32 +3709,32 @@
         <v>2</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E56" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B57">
         <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E57" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B58">
         <v>17</v>
@@ -3743,15 +3743,15 @@
         <v>4</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B59">
         <v>17</v>
@@ -3760,15 +3760,15 @@
         <v>4</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E59" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B60">
         <v>17</v>
@@ -3777,15 +3777,15 @@
         <v>4</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E60" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B61">
         <v>18</v>
@@ -3794,15 +3794,15 @@
         <v>13</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E61" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B62">
         <v>18</v>
@@ -3811,15 +3811,15 @@
         <v>13</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B63">
         <v>18</v>
@@ -3828,15 +3828,15 @@
         <v>13</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B64">
         <v>18</v>
@@ -3845,83 +3845,83 @@
         <v>13</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B65">
         <v>19</v>
       </c>
       <c r="C65" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E65" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B66">
         <v>19</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E66" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B67">
         <v>19</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B68">
         <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B69">
         <v>19</v>
@@ -3930,32 +3930,32 @@
         <v>16</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B70">
         <v>19</v>
       </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B71">
         <v>19</v>
@@ -3964,49 +3964,49 @@
         <v>10</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E71" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B72">
         <v>19</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B73">
         <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E73" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B74">
         <v>19</v>
@@ -4015,15 +4015,15 @@
         <v>3</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B75">
         <v>19</v>
@@ -4032,32 +4032,32 @@
         <v>1</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E75" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B76">
         <v>19</v>
       </c>
       <c r="C76" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E76" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B77">
         <v>20</v>
@@ -4066,15 +4066,15 @@
         <v>16</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B78">
         <v>20</v>
@@ -4083,32 +4083,32 @@
         <v>16</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E78" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B79">
         <v>20</v>
       </c>
       <c r="C79" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E79" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B80">
         <v>20</v>
@@ -4117,15 +4117,15 @@
         <v>0</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E80" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B81">
         <v>20</v>
@@ -4134,66 +4134,66 @@
         <v>9</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E81" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B82">
         <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E82" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B83">
         <v>21</v>
       </c>
       <c r="C83" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E83" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B84">
         <v>21</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E84" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B85">
         <v>21</v>
@@ -4202,32 +4202,32 @@
         <v>9</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E85" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B86">
         <v>21</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E86" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B87">
         <v>21</v>
@@ -4236,15 +4236,15 @@
         <v>13</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B88">
         <v>21</v>
@@ -4253,49 +4253,49 @@
         <v>13</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E88" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B89">
         <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B90">
         <v>21</v>
       </c>
       <c r="C90" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E90" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B91">
         <v>21</v>
@@ -4304,49 +4304,49 @@
         <v>16</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E91" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B92">
         <v>21</v>
       </c>
       <c r="C92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E92" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B93">
         <v>21</v>
       </c>
       <c r="C93" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B94">
         <v>22</v>
@@ -4355,15 +4355,15 @@
         <v>0</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E94" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B95">
         <v>22</v>
@@ -4372,15 +4372,15 @@
         <v>0</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E95" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B96">
         <v>22</v>
@@ -4389,15 +4389,15 @@
         <v>0</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E96" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B97">
         <v>22</v>
@@ -4406,49 +4406,49 @@
         <v>0</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E97" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B98">
         <v>23</v>
       </c>
       <c r="C98" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E98" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B99">
         <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E99" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B100">
         <v>23</v>
@@ -4457,15 +4457,15 @@
         <v>9</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E100" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B101">
         <v>23</v>
@@ -4474,15 +4474,15 @@
         <v>17</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E101" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B102">
         <v>23</v>
@@ -4491,15 +4491,15 @@
         <v>17</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E102" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B103">
         <v>23</v>
@@ -4508,15 +4508,15 @@
         <v>9</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B104">
         <v>23</v>
@@ -4525,15 +4525,15 @@
         <v>17</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E104" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B105">
         <v>23</v>
@@ -4542,49 +4542,49 @@
         <v>17</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B106">
         <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B107">
         <v>24</v>
       </c>
       <c r="C107" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E107" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B108">
         <v>24</v>
@@ -4593,15 +4593,15 @@
         <v>13</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E108" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B109">
         <v>24</v>
@@ -4610,32 +4610,32 @@
         <v>17</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B110">
         <v>25</v>
       </c>
       <c r="C110" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E110" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B111">
         <v>25</v>
@@ -4644,15 +4644,15 @@
         <v>0</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E111" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B112">
         <v>26</v>
@@ -4661,66 +4661,66 @@
         <v>16</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E112" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B113">
         <v>27</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B114">
         <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E114" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B115">
         <v>27</v>
       </c>
       <c r="C115" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E115" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B116">
         <v>28</v>
@@ -4729,15 +4729,15 @@
         <v>8</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E116" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B117">
         <v>28</v>
@@ -4746,15 +4746,15 @@
         <v>0</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E117" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B118">
         <v>28</v>
@@ -4763,15 +4763,15 @@
         <v>0</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B119">
         <v>28</v>
@@ -4780,15 +4780,15 @@
         <v>0</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E119" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B120">
         <v>28</v>
@@ -4797,15 +4797,15 @@
         <v>0</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E120" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B121">
         <v>28</v>
@@ -4814,32 +4814,32 @@
         <v>0</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E121" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B122">
         <v>28</v>
       </c>
       <c r="C122" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E122" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B123">
         <v>28</v>
@@ -4848,49 +4848,49 @@
         <v>17</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E123" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B124">
         <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E124" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B125">
         <v>28</v>
       </c>
       <c r="C125" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E125" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B126">
         <v>29</v>
@@ -4899,49 +4899,49 @@
         <v>12</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B127">
         <v>29</v>
       </c>
       <c r="C127" t="s">
+        <v>210</v>
+      </c>
+      <c r="D127" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D127" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="E127" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B128">
         <v>29</v>
       </c>
       <c r="C128" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E128" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B129">
         <v>29</v>
@@ -4950,66 +4950,66 @@
         <v>11</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E129" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B130">
         <v>29</v>
       </c>
       <c r="C130" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E130" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B131">
         <v>30</v>
       </c>
       <c r="C131" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E131" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B132">
         <v>30</v>
       </c>
       <c r="C132" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E132" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B133">
         <v>30</v>
@@ -5018,32 +5018,32 @@
         <v>16</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E133" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B134">
         <v>30</v>
       </c>
       <c r="C134" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E134" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B135">
         <v>30</v>
@@ -5052,15 +5052,15 @@
         <v>16</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E135" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B136">
         <v>30</v>
@@ -5069,15 +5069,15 @@
         <v>4</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E136" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B137">
         <v>31</v>
@@ -5086,15 +5086,15 @@
         <v>4</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E137" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B138">
         <v>31</v>
@@ -5103,32 +5103,32 @@
         <v>4</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E138" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B139">
         <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E139" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B140">
         <v>31</v>
@@ -5137,15 +5137,15 @@
         <v>0</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E140" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B141">
         <v>31</v>
@@ -5154,83 +5154,83 @@
         <v>0</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E141" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B142">
         <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E142" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B143">
         <v>31</v>
       </c>
       <c r="C143" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E143" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B144">
         <v>32</v>
       </c>
       <c r="C144" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E144" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B145">
         <v>32</v>
       </c>
       <c r="C145" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E145" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B146">
         <v>34</v>
@@ -5239,15 +5239,15 @@
         <v>0</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E146" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B147">
         <v>34</v>
@@ -5256,100 +5256,100 @@
         <v>17</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E147" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B148">
         <v>34</v>
       </c>
       <c r="C148" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E148" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B149">
         <v>34</v>
       </c>
       <c r="C149" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E149" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B150">
         <v>34</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E150" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B151">
         <v>34</v>
       </c>
       <c r="C151" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E151" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B152">
         <v>34</v>
       </c>
       <c r="C152" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E152" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B153">
         <v>38</v>
@@ -5358,32 +5358,32 @@
         <v>10</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E153" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B154">
         <v>38</v>
       </c>
       <c r="C154" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E154" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B155">
         <v>38</v>
@@ -5392,15 +5392,15 @@
         <v>3</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E155" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B156">
         <v>38</v>
@@ -5409,66 +5409,66 @@
         <v>8</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E156" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B157">
         <v>42</v>
       </c>
       <c r="C157" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E157" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B158">
         <v>42</v>
       </c>
       <c r="C158" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E158" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B159">
         <v>43</v>
       </c>
       <c r="C159" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E159" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B160">
         <v>43</v>
@@ -5477,15 +5477,15 @@
         <v>17</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E160" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B161">
         <v>44</v>
@@ -5494,32 +5494,32 @@
         <v>12</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B162">
         <v>45</v>
       </c>
       <c r="C162" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E162" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B163">
         <v>58</v>
@@ -5528,15 +5528,15 @@
         <v>0</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E163" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B164">
         <v>58</v>
@@ -5545,15 +5545,15 @@
         <v>0</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E164" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B165">
         <v>58</v>
@@ -5562,66 +5562,66 @@
         <v>0</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E165" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B166">
         <v>59</v>
       </c>
       <c r="C166" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E166" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B167">
         <v>59</v>
       </c>
       <c r="C167" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E167" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B168">
         <v>59</v>
       </c>
       <c r="C168" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E168" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B169">
         <v>59</v>
@@ -5630,15 +5630,15 @@
         <v>16</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E169" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B170">
         <v>62</v>
@@ -5647,15 +5647,15 @@
         <v>16</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B171">
         <v>62</v>
@@ -5664,15 +5664,15 @@
         <v>16</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E171" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B172">
         <v>62</v>
@@ -5681,15 +5681,15 @@
         <v>16</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B173">
         <v>62</v>
@@ -5698,15 +5698,15 @@
         <v>16</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E173" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B174">
         <v>65</v>
@@ -5715,49 +5715,49 @@
         <v>16</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E174" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B175">
         <v>65</v>
       </c>
       <c r="C175" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E175" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B176">
         <v>66</v>
       </c>
       <c r="C176" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E176" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B177">
         <v>66</v>
@@ -5766,15 +5766,15 @@
         <v>4</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E177" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B178">
         <v>66</v>
@@ -5783,29 +5783,29 @@
         <v>10</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E178" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B179">
         <v>66</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E179" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B180">
         <v>66</v>
@@ -5814,15 +5814,15 @@
         <v>4</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E180" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B181">
         <v>66</v>
@@ -5831,15 +5831,15 @@
         <v>3</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E181" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B182">
         <v>66</v>
@@ -5848,15 +5848,15 @@
         <v>3</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E182" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B183">
         <v>66</v>
@@ -5865,15 +5865,15 @@
         <v>3</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E183" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B184">
         <v>69</v>
@@ -5882,15 +5882,15 @@
         <v>7</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E184" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="185" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B185">
         <v>69</v>
@@ -5899,15 +5899,15 @@
         <v>7</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E185" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="186" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B186">
         <v>69</v>
@@ -5916,15 +5916,15 @@
         <v>7</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E186" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B187">
         <v>69</v>
@@ -5933,49 +5933,49 @@
         <v>12</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E187" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B188">
         <v>69</v>
       </c>
       <c r="C188" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E188" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B189">
         <v>69</v>
       </c>
       <c r="C189" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E189" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B190">
         <v>69</v>
@@ -5984,15 +5984,15 @@
         <v>14</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E190" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B191">
         <v>69</v>
@@ -6001,32 +6001,32 @@
         <v>17</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E191" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B192">
         <v>69</v>
       </c>
       <c r="C192" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E192" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B193">
         <v>69</v>
@@ -6035,49 +6035,49 @@
         <v>11</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E193" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B194">
         <v>72</v>
       </c>
       <c r="C194" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E194" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B195">
         <v>72</v>
       </c>
       <c r="C195" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E195" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B196">
         <v>72</v>
@@ -6086,83 +6086,83 @@
         <v>9</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E196" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="197" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B197">
         <v>72</v>
       </c>
       <c r="C197" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E197" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B198">
         <v>72</v>
       </c>
       <c r="C198" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E198" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B199">
         <v>72</v>
       </c>
       <c r="C199" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E199" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="200" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B200">
         <v>74</v>
       </c>
       <c r="C200" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E200" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B201">
         <v>74</v>
@@ -6171,15 +6171,15 @@
         <v>17</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B202">
         <v>82</v>
@@ -6188,32 +6188,32 @@
         <v>0</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E202" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B203">
         <v>82</v>
       </c>
       <c r="C203" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E203" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B204">
         <v>82</v>
@@ -6222,15 +6222,15 @@
         <v>16</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E204" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B205">
         <v>82</v>
@@ -6239,15 +6239,15 @@
         <v>16</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E205" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B206">
         <v>82</v>
@@ -6256,15 +6256,15 @@
         <v>3.4</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E206" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B207">
         <v>82</v>
@@ -6273,15 +6273,15 @@
         <v>13</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E207" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B208">
         <v>82</v>
@@ -6290,15 +6290,15 @@
         <v>16</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E208" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="209" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B209">
         <v>82</v>
@@ -6307,15 +6307,15 @@
         <v>17</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E209" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="210" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B210">
         <v>82</v>
@@ -6324,32 +6324,32 @@
         <v>17</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E210" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="211" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B211">
         <v>82</v>
       </c>
       <c r="C211" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E211" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="212" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B212">
         <v>82</v>
@@ -6358,15 +6358,15 @@
         <v>16</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E212" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="213" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B213">
         <v>82</v>
@@ -6375,83 +6375,83 @@
         <v>16</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E213" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="214" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B214">
         <v>89</v>
       </c>
       <c r="C214" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E214" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="215" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B215">
         <v>93</v>
       </c>
       <c r="C215" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E215" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="216" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B216">
         <v>93</v>
       </c>
       <c r="C216" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E216" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B217">
         <v>93</v>
       </c>
       <c r="C217" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E217" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="218" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B218">
         <v>93</v>
@@ -6460,32 +6460,32 @@
         <v>2</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E218" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="219" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B219">
         <v>93</v>
       </c>
       <c r="C219" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E219" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="220" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B220">
         <v>96</v>
@@ -6494,15 +6494,15 @@
         <v>0</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E220" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="221" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B221">
         <v>97</v>
@@ -6511,32 +6511,32 @@
         <v>0</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E221" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B222">
         <v>97</v>
       </c>
       <c r="C222" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E222" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="223" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B223">
         <v>97</v>
@@ -6545,12 +6545,12 @@
         <v>0</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="224" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B224">
         <v>98</v>
@@ -6559,32 +6559,32 @@
         <v>17</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E224" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B225">
         <v>98</v>
       </c>
       <c r="C225" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E225" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B226">
         <v>98</v>
@@ -6593,165 +6593,165 @@
         <v>8</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E226" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B227">
         <v>99</v>
       </c>
       <c r="C227" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E227" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B228">
         <v>99</v>
       </c>
       <c r="C228" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E228" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B229">
         <v>99</v>
       </c>
       <c r="C229" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E229" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="230" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B230">
         <v>99</v>
       </c>
       <c r="C230" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E230" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B231">
         <v>99</v>
       </c>
       <c r="C231" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E231" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="232" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B232">
         <v>99</v>
       </c>
       <c r="C232" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B233">
         <v>100</v>
       </c>
       <c r="C233" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E233" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="234" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B234">
         <v>100</v>
       </c>
       <c r="C234" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E234" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="235" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B235">
         <v>100</v>
       </c>
       <c r="C235" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E235" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B236">
         <v>6</v>
@@ -6760,15 +6760,15 @@
         <v>0</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E236" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="237" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B237">
         <v>6</v>
@@ -6777,15 +6777,15 @@
         <v>0</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E237" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="238" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B238">
         <v>6</v>
@@ -6794,15 +6794,15 @@
         <v>0</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E238" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="239" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B239">
         <v>6</v>
@@ -6811,32 +6811,32 @@
         <v>0</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E239" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="240" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B240">
         <v>6</v>
       </c>
       <c r="C240" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E240" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="241" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B241">
         <v>6</v>
@@ -6845,32 +6845,32 @@
         <v>9</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E241" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="242" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B242">
         <v>6</v>
       </c>
       <c r="C242" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E242" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B243">
         <v>6</v>
@@ -6879,15 +6879,15 @@
         <v>0</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E243" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="244" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B244">
         <v>8</v>
@@ -6896,15 +6896,15 @@
         <v>0</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E244" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="245" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B245">
         <v>8</v>
@@ -6913,15 +6913,15 @@
         <v>16</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E245" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="246" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B246">
         <v>8</v>
@@ -6930,15 +6930,15 @@
         <v>16</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E246" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="247" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B247">
         <v>8</v>
@@ -6947,46 +6947,46 @@
         <v>0</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E247" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="248" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B248">
         <v>9</v>
       </c>
       <c r="C248" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E248" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="249" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B249">
         <v>9</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E249" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="250" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B250">
         <v>30</v>
@@ -6995,15 +6995,15 @@
         <v>10</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E250" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B251">
         <v>30</v>
@@ -7012,15 +7012,15 @@
         <v>10</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E251" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="252" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B252">
         <v>30</v>
@@ -7029,15 +7029,15 @@
         <v>10</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E252" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="253" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B253">
         <v>30</v>
@@ -7046,15 +7046,15 @@
         <v>10</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E253" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="254" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B254">
         <v>30</v>
@@ -7063,15 +7063,15 @@
         <v>10</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E254" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B255">
         <v>30</v>
@@ -7080,15 +7080,15 @@
         <v>10</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E255" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="256" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B256">
         <v>30</v>
@@ -7097,15 +7097,15 @@
         <v>10</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E256" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B257">
         <v>30</v>
@@ -7114,32 +7114,32 @@
         <v>10</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E257" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="258" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B258">
         <v>30</v>
       </c>
       <c r="C258" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E258" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="259" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B259">
         <v>30</v>
@@ -7148,15 +7148,15 @@
         <v>10</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E259" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B260">
         <v>31</v>
@@ -7165,15 +7165,15 @@
         <v>10</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E260" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="261" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B261">
         <v>31</v>
@@ -7182,185 +7182,185 @@
         <v>10</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E261" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="262" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B262">
         <v>31</v>
       </c>
       <c r="C262" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E262" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B263">
         <v>31</v>
       </c>
       <c r="C263" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E263" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="264" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B264">
         <v>31</v>
       </c>
       <c r="C264" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E264" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B265">
         <v>31</v>
       </c>
       <c r="C265" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E265" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="266" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B266">
         <v>31</v>
       </c>
       <c r="C266" t="s">
+        <v>397</v>
+      </c>
+      <c r="D266" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="D266" s="6" t="s">
-        <v>401</v>
-      </c>
       <c r="E266" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B267">
         <v>31</v>
       </c>
       <c r="C267" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E267" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="268" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B268">
         <v>31</v>
       </c>
       <c r="C268" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="269" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B269">
         <v>31</v>
       </c>
       <c r="C269" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E269" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="270" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B270">
         <v>31</v>
       </c>
       <c r="C270" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E270" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B271">
         <v>31</v>
       </c>
       <c r="C271" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E271" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="272" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B272">
         <v>32</v>
@@ -7369,15 +7369,15 @@
         <v>11</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E272" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="273" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B273">
         <v>32</v>
@@ -7386,15 +7386,15 @@
         <v>11</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E273" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="274" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B274">
         <v>32</v>
@@ -7403,15 +7403,15 @@
         <v>11</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E274" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="275" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B275">
         <v>32</v>
@@ -7420,32 +7420,32 @@
         <v>11</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E275" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="276" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B276">
         <v>32</v>
       </c>
       <c r="C276" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E276" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="277" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B277">
         <v>32</v>
@@ -7454,15 +7454,15 @@
         <v>11</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E277" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B278">
         <v>32</v>
@@ -7471,15 +7471,15 @@
         <v>11</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E278" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="279" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B279">
         <v>32</v>
@@ -7488,15 +7488,15 @@
         <v>11</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E279" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B280">
         <v>32</v>
@@ -7505,32 +7505,32 @@
         <v>11</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E280" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="281" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B281">
         <v>32</v>
       </c>
       <c r="C281" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E281" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="282" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B282">
         <v>32</v>
@@ -7539,66 +7539,66 @@
         <v>11</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E282" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B283">
         <v>33</v>
       </c>
       <c r="C283" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E283" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="284" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B284">
         <v>33</v>
       </c>
       <c r="C284" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E284" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="285" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B285">
         <v>33</v>
       </c>
       <c r="C285" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E285" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B286">
         <v>33</v>
@@ -7607,32 +7607,32 @@
         <v>11</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E286" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="287" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B287">
         <v>33</v>
       </c>
       <c r="C287" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E287" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="288" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B288">
         <v>33</v>
@@ -7641,15 +7641,15 @@
         <v>11</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E288" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="289" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B289">
         <v>33</v>
@@ -7658,15 +7658,15 @@
         <v>11</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E289" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="290" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B290">
         <v>33</v>
@@ -7675,15 +7675,15 @@
         <v>11</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E290" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="291" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B291">
         <v>33</v>
@@ -7692,49 +7692,49 @@
         <v>11</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E291" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="292" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B292">
         <v>33</v>
       </c>
       <c r="C292" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E292" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="293" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B293">
         <v>33</v>
       </c>
       <c r="C293" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E293" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="294" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B294">
         <v>34</v>
@@ -7743,15 +7743,15 @@
         <v>12</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E294" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="295" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B295">
         <v>34</v>
@@ -7760,15 +7760,15 @@
         <v>12</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E295" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="296" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B296">
         <v>34</v>
@@ -7777,15 +7777,15 @@
         <v>12</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E296" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="297" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B297">
         <v>34</v>
@@ -7794,32 +7794,32 @@
         <v>12</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E297" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="298" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B298">
         <v>34</v>
       </c>
       <c r="C298" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E298" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="299" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B299">
         <v>34</v>
@@ -7828,15 +7828,15 @@
         <v>12</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E299" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="300" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B300">
         <v>34</v>
@@ -7845,15 +7845,15 @@
         <v>12</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E300" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="301" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B301">
         <v>34</v>
@@ -7862,49 +7862,49 @@
         <v>12</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E301" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="302" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B302">
         <v>34</v>
       </c>
       <c r="C302" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E302" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="303" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B303">
         <v>34</v>
       </c>
       <c r="C303" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E303" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B304">
         <v>34</v>
@@ -7913,32 +7913,32 @@
         <v>12</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E304" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="305" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B305">
         <v>34</v>
       </c>
       <c r="C305" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E305" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B306">
         <v>35</v>
@@ -7946,22 +7946,22 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -7983,16 +7983,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8000,13 +8000,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="61.9" x14ac:dyDescent="0.45">
@@ -8014,13 +8014,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="31.5" x14ac:dyDescent="0.45">
@@ -8028,13 +8028,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8042,13 +8042,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8056,13 +8056,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8070,13 +8070,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.45">
@@ -8084,13 +8084,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="31.5" x14ac:dyDescent="0.45">
@@ -8098,13 +8098,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8112,13 +8112,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="51.75" x14ac:dyDescent="0.45">
@@ -8126,13 +8126,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
@@ -8140,13 +8140,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8154,13 +8154,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8168,13 +8168,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8182,13 +8182,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="41.65" x14ac:dyDescent="0.45">
@@ -8196,13 +8196,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
@@ -8210,13 +8210,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="61.9" x14ac:dyDescent="0.45">
@@ -8224,13 +8224,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="41.65" x14ac:dyDescent="0.45">
@@ -8238,19 +8238,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C26" s="16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -8263,19 +8263,19 @@
         <v>0</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="7">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="7">
         <v>12</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
@@ -8283,19 +8283,19 @@
         <v>1</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="7">
         <v>7</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" s="7">
         <v>13</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.45">
@@ -8303,19 +8303,19 @@
         <v>2</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" s="7">
         <v>8</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" s="7">
         <v>14</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="54.75" x14ac:dyDescent="0.45">
@@ -8323,19 +8323,19 @@
         <v>3</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E30" s="7">
         <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G30" s="7">
         <v>15</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="57" x14ac:dyDescent="0.45">
@@ -8343,19 +8343,19 @@
         <v>4</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" s="7">
         <v>10</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31" s="7">
         <v>16</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="71.650000000000006" thickBot="1" x14ac:dyDescent="0.5">
@@ -8363,19 +8363,19 @@
         <v>5</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E32" s="13">
         <v>11</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G32" s="13">
         <v>17</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
+++ b/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/cpaltat_upv_edu_es/Documents/TFM/Data/Annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3110" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CD857D7-1AF6-4D00-9423-CB5518C61292}"/>
+  <xr:revisionPtr revIDLastSave="3179" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DD72B76-8E24-42AC-BD97-B349249ABF49}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{49184B03-C425-4292-8179-3E0C1E060977}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="ODS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Argument annotations'!$A$1:$I$1015</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Argument annotations'!$A$1:$I$1018</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2606" uniqueCount="1366">
   <si>
     <t>Page</t>
   </si>
@@ -4828,18 +4828,12 @@
     <t>Accounting for these spillovers becomes crucial for an accurate assessment of contributions towards sustainable development.</t>
   </si>
   <si>
-    <t>1, 12</t>
-  </si>
-  <si>
     <t>For instance, in some G20 economies (e.g., Germany, France, the UK), offshore GHG emissions are more than 40 percent of their total GHG footprint</t>
   </si>
   <si>
     <t>Ultimately, curbing negative spillovers requires multilateral solutions, especially between resource-rich and labor-rich countries with high income consumer countries</t>
   </si>
   <si>
-    <t>12, 8</t>
-  </si>
-  <si>
     <t>Given the global nature of this challenge, the G20 is a suitable platform for tackling international spillovers.</t>
   </si>
   <si>
@@ -4927,9 +4921,6 @@
     <t>The 2023 Action Plan, under the Indian presidency, called for action in three key areas: digital transformation, gender equality, and just transitions</t>
   </si>
   <si>
-    <t>9, 5, 7, 8, 13</t>
-  </si>
-  <si>
     <t>Developed within the Development Working Group, the Action Plans aim to enhance policy coherence and coordination across all G20 work streams for the SDGs achievement.Thus, it seems logical to integrate the issue of spillover effects into the next Action Plan update.</t>
   </si>
   <si>
@@ -4952,6 +4943,27 @@
   </si>
   <si>
     <t>Under a positive scenario, the G20 (especially through its Development Working Group) will be able to foster a high-level policy dialogue on the importance of international spillover effects as an important factor to accelerate the achievement of the SDGs.</t>
+  </si>
+  <si>
+    <t>The adoption of the 2030 Agenda provided a shared pathway towards sustainable development via the achievement of 17 Sustainable Development Goals (SDGs) by 2030.</t>
+  </si>
+  <si>
+    <t>12, 0</t>
+  </si>
+  <si>
+    <t>8, 13</t>
+  </si>
+  <si>
+    <t>9, 5, 13, 10</t>
+  </si>
+  <si>
+    <t>G20 countries should also track these effects against time-bound quantitative targets to hold themselves accountable for mitigating negative spillovers, such as resource depletion (e.g., material footprints)</t>
+  </si>
+  <si>
+    <t>12, 8, 17</t>
+  </si>
+  <si>
+    <t>1, 12, 13</t>
   </si>
 </sst>
 </file>
@@ -5530,7 +5542,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I1015"/>
+  <dimension ref="A1:I1018"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="43.06640625" bestFit="1" customWidth="1"/>
@@ -8824,7 +8836,7 @@
     </row>
     <row r="236" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B236">
         <v>6</v>
@@ -13440,6 +13452,9 @@
       </c>
     </row>
     <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A566" t="s">
+        <v>449</v>
+      </c>
       <c r="B566">
         <v>21</v>
       </c>
@@ -14628,7 +14643,7 @@
     </row>
     <row r="651" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
-        <v>877</v>
+        <v>449</v>
       </c>
       <c r="B651">
         <v>10</v>
@@ -14837,6 +14852,9 @@
       </c>
     </row>
     <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A666" t="s">
+        <v>877</v>
+      </c>
       <c r="B666">
         <v>11</v>
       </c>
@@ -15170,6 +15188,9 @@
       </c>
     </row>
     <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A690" t="s">
+        <v>877</v>
+      </c>
       <c r="B690">
         <v>15</v>
       </c>
@@ -15251,6 +15272,9 @@
       </c>
     </row>
     <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A696" t="s">
+        <v>877</v>
+      </c>
       <c r="B696">
         <v>15</v>
       </c>
@@ -15332,6 +15356,9 @@
       </c>
     </row>
     <row r="702" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A702" t="s">
+        <v>877</v>
+      </c>
       <c r="B702">
         <v>15</v>
       </c>
@@ -15413,6 +15440,9 @@
       </c>
     </row>
     <row r="708" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A708" t="s">
+        <v>877</v>
+      </c>
       <c r="B708">
         <v>16</v>
       </c>
@@ -15494,6 +15524,9 @@
       </c>
     </row>
     <row r="714" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A714" t="s">
+        <v>877</v>
+      </c>
       <c r="B714">
         <v>16</v>
       </c>
@@ -15575,6 +15608,9 @@
       </c>
     </row>
     <row r="720" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A720" t="s">
+        <v>877</v>
+      </c>
       <c r="B720">
         <v>17</v>
       </c>
@@ -15642,6 +15678,9 @@
       </c>
     </row>
     <row r="725" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A725" t="s">
+        <v>877</v>
+      </c>
       <c r="B725">
         <v>17</v>
       </c>
@@ -15723,6 +15762,9 @@
       </c>
     </row>
     <row r="731" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A731" t="s">
+        <v>877</v>
+      </c>
       <c r="B731">
         <v>18</v>
       </c>
@@ -15804,6 +15846,9 @@
       </c>
     </row>
     <row r="737" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+      <c r="A737" t="s">
+        <v>877</v>
+      </c>
       <c r="B737">
         <v>19</v>
       </c>
@@ -16911,9 +16956,9 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="817" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A817" t="s">
-        <v>1090</v>
+        <v>877</v>
       </c>
       <c r="B817">
         <v>4</v>
@@ -16925,7 +16970,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="818" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
         <v>1090</v>
       </c>
@@ -16939,7 +16984,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="819" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A819" t="s">
         <v>1090</v>
       </c>
@@ -16953,7 +16998,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="820" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A820" t="s">
         <v>1090</v>
       </c>
@@ -16967,7 +17012,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="821" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821" t="s">
         <v>1090</v>
       </c>
@@ -16981,7 +17026,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="822" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A822" t="s">
         <v>1090</v>
       </c>
@@ -16995,7 +17040,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="823" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A823" t="s">
         <v>1090</v>
       </c>
@@ -17009,7 +17054,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="824" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824" t="s">
         <v>1090</v>
       </c>
@@ -17023,7 +17068,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="825" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825" t="s">
         <v>1090</v>
       </c>
@@ -17037,7 +17082,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="826" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826" t="s">
         <v>1090</v>
       </c>
@@ -17051,7 +17096,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="827" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A827" t="s">
         <v>1090</v>
       </c>
@@ -17065,7 +17110,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="828" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A828" t="s">
         <v>1090</v>
       </c>
@@ -17079,7 +17124,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829" t="s">
         <v>1090</v>
       </c>
@@ -17093,7 +17138,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="830" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A830" t="s">
         <v>1090</v>
       </c>
@@ -17107,7 +17152,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="831" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A831" t="s">
         <v>1090</v>
       </c>
@@ -17121,7 +17166,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="832" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A832" t="s">
         <v>1090</v>
       </c>
@@ -17135,7 +17180,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="833" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833" t="s">
         <v>1090</v>
       </c>
@@ -17149,7 +17194,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="834" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A834" t="s">
         <v>1090</v>
       </c>
@@ -17163,7 +17208,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="835" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835" t="s">
         <v>1090</v>
       </c>
@@ -17177,7 +17222,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="836" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836" t="s">
         <v>1090</v>
       </c>
@@ -17191,7 +17236,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="837" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837" t="s">
         <v>1090</v>
       </c>
@@ -17205,7 +17250,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="838" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="838" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A838" t="s">
         <v>1090</v>
       </c>
@@ -17219,7 +17264,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="839" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A839" t="s">
         <v>1090</v>
       </c>
@@ -17233,7 +17278,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="840" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A840" t="s">
         <v>1090</v>
       </c>
@@ -17247,7 +17292,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="841" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A841" t="s">
         <v>1090</v>
       </c>
@@ -17261,7 +17306,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="842" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842" t="s">
         <v>1090</v>
       </c>
@@ -17275,7 +17320,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="843" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A843" t="s">
         <v>1090</v>
       </c>
@@ -17289,7 +17334,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="844" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A844" t="s">
         <v>1090</v>
       </c>
@@ -17303,7 +17348,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="845" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845" t="s">
         <v>1090</v>
       </c>
@@ -17317,7 +17362,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="846" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A846" t="s">
         <v>1090</v>
       </c>
@@ -17331,7 +17376,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="847" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A847" t="s">
         <v>1090</v>
       </c>
@@ -17345,7 +17390,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="848" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A848" t="s">
         <v>1090</v>
       </c>
@@ -17359,7 +17404,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="849" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849" t="s">
         <v>1090</v>
       </c>
@@ -17373,7 +17418,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="850" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A850" t="s">
         <v>1090</v>
       </c>
@@ -17387,7 +17432,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="851" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A851" t="s">
         <v>1090</v>
       </c>
@@ -17401,7 +17446,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="852" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="852" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A852" t="s">
         <v>1090</v>
       </c>
@@ -17415,7 +17460,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="853" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A853" t="s">
         <v>1090</v>
       </c>
@@ -17429,7 +17474,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="854" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854" t="s">
         <v>1090</v>
       </c>
@@ -17443,7 +17488,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="855" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A855" t="s">
         <v>1090</v>
       </c>
@@ -17457,7 +17502,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="856" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A856" t="s">
         <v>1090</v>
       </c>
@@ -17471,7 +17516,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="857" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A857" t="s">
         <v>1090</v>
       </c>
@@ -17485,7 +17530,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="858" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858" t="s">
         <v>1090</v>
       </c>
@@ -17499,7 +17544,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="859" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A859" t="s">
         <v>1090</v>
       </c>
@@ -17513,7 +17558,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="860" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A860" t="s">
         <v>1090</v>
       </c>
@@ -17527,7 +17572,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="861" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>1090</v>
       </c>
@@ -17541,7 +17586,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="862" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>1090</v>
       </c>
@@ -17555,7 +17600,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="863" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A863" t="s">
         <v>1090</v>
       </c>
@@ -17569,7 +17614,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="864" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A864" t="s">
         <v>1090</v>
       </c>
@@ -17583,7 +17628,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="865" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A865" t="s">
         <v>1090</v>
       </c>
@@ -17597,7 +17642,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="866" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>1090</v>
       </c>
@@ -17611,7 +17656,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="867" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A867" t="s">
         <v>1090</v>
       </c>
@@ -17625,7 +17670,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="868" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>1090</v>
       </c>
@@ -17639,7 +17684,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="869" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>1090</v>
       </c>
@@ -17653,7 +17698,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="870" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>1090</v>
       </c>
@@ -17667,7 +17712,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="871" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A871" t="s">
         <v>1090</v>
       </c>
@@ -17681,7 +17726,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="872" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A872" t="s">
         <v>1090</v>
       </c>
@@ -17695,7 +17740,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="873" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A873" t="s">
         <v>1090</v>
       </c>
@@ -17709,7 +17754,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="874" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>1090</v>
       </c>
@@ -17723,7 +17768,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="875" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>1090</v>
       </c>
@@ -17737,7 +17782,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="876" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A876" t="s">
         <v>1090</v>
       </c>
@@ -17751,7 +17796,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="877" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A877" t="s">
         <v>1090</v>
       </c>
@@ -17765,7 +17810,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="878" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A878" t="s">
         <v>1090</v>
       </c>
@@ -17779,7 +17824,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="879" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A879" t="s">
         <v>1090</v>
       </c>
@@ -17793,7 +17838,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="880" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A880" t="s">
         <v>1090</v>
       </c>
@@ -17807,7 +17852,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="881" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A881" t="s">
         <v>1090</v>
       </c>
@@ -17821,7 +17866,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="882" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A882" t="s">
         <v>1090</v>
       </c>
@@ -17835,7 +17880,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="883" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="883" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A883" t="s">
         <v>1090</v>
       </c>
@@ -17849,7 +17894,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A884" t="s">
         <v>1090</v>
       </c>
@@ -17863,7 +17908,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="885" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A885" t="s">
         <v>1090</v>
       </c>
@@ -17877,7 +17922,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A886" t="s">
         <v>1090</v>
       </c>
@@ -17891,7 +17936,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A887" t="s">
         <v>1090</v>
       </c>
@@ -17905,7 +17950,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="888" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A888" t="s">
         <v>1090</v>
       </c>
@@ -17919,7 +17964,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="889" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A889" t="s">
         <v>1090</v>
       </c>
@@ -17933,7 +17978,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="890" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A890" t="s">
         <v>1090</v>
       </c>
@@ -17947,7 +17992,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A891" t="s">
         <v>1090</v>
       </c>
@@ -17961,7 +18006,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="892" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A892" t="s">
         <v>1090</v>
       </c>
@@ -17975,7 +18020,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A893" t="s">
         <v>1090</v>
       </c>
@@ -17989,7 +18034,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A894" t="s">
         <v>1090</v>
       </c>
@@ -18003,7 +18048,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="895" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A895" t="s">
         <v>1090</v>
       </c>
@@ -18017,7 +18062,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="896" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A896" t="s">
         <v>1090</v>
       </c>
@@ -18031,7 +18076,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="897" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A897" t="s">
         <v>1090</v>
       </c>
@@ -18045,7 +18090,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="898" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A898" t="s">
         <v>1090</v>
       </c>
@@ -18059,7 +18104,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="899" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A899" t="s">
         <v>1090</v>
       </c>
@@ -18073,7 +18118,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="900" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A900" t="s">
         <v>1090</v>
       </c>
@@ -18087,7 +18132,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="901" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="901" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A901" t="s">
         <v>1090</v>
       </c>
@@ -18101,7 +18146,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="902" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A902" t="s">
         <v>1090</v>
       </c>
@@ -18115,7 +18160,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="903" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="903" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A903" t="s">
         <v>1090</v>
       </c>
@@ -18129,7 +18174,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="904" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="904" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A904" t="s">
         <v>1090</v>
       </c>
@@ -18143,7 +18188,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="905" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="905" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A905" t="s">
         <v>1090</v>
       </c>
@@ -18157,7 +18202,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="906" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A906" t="s">
         <v>1090</v>
       </c>
@@ -18171,7 +18216,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="907" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A907" t="s">
         <v>1090</v>
       </c>
@@ -18185,7 +18230,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="908" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="908" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A908" t="s">
         <v>1090</v>
       </c>
@@ -18199,7 +18244,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="909" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="909" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A909" t="s">
         <v>1090</v>
       </c>
@@ -18213,7 +18258,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="910" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A910" t="s">
         <v>1090</v>
       </c>
@@ -18227,7 +18272,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="911" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A911" t="s">
         <v>1090</v>
       </c>
@@ -18241,7 +18286,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="912" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A912" t="s">
         <v>1090</v>
       </c>
@@ -18255,7 +18300,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="913" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A913" t="s">
         <v>1090</v>
       </c>
@@ -18269,7 +18314,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="914" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A914" t="s">
         <v>1090</v>
       </c>
@@ -18283,7 +18328,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="915" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A915" t="s">
         <v>1090</v>
       </c>
@@ -18297,7 +18342,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="916" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A916" t="s">
         <v>1090</v>
       </c>
@@ -18311,7 +18356,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="917" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A917" t="s">
         <v>1090</v>
       </c>
@@ -18325,7 +18370,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="918" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A918" t="s">
         <v>1090</v>
       </c>
@@ -18339,7 +18384,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="919" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="919" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A919" t="s">
         <v>1090</v>
       </c>
@@ -18353,7 +18398,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="920" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A920" t="s">
         <v>1090</v>
       </c>
@@ -18367,7 +18412,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="921" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A921" t="s">
         <v>1090</v>
       </c>
@@ -18381,7 +18426,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="922" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="922" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A922" t="s">
         <v>1090</v>
       </c>
@@ -18395,7 +18440,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="923" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="923" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A923" t="s">
         <v>1090</v>
       </c>
@@ -18409,7 +18454,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="924" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="924" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A924" t="s">
         <v>1090</v>
       </c>
@@ -18423,7 +18468,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="925" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="925" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A925" t="s">
         <v>1090</v>
       </c>
@@ -18437,7 +18482,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="926" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="926" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A926" t="s">
         <v>1090</v>
       </c>
@@ -18451,7 +18496,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="927" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="927" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A927" t="s">
         <v>1090</v>
       </c>
@@ -18465,7 +18510,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="928" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="928" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A928" t="s">
         <v>1090</v>
       </c>
@@ -18479,7 +18524,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="929" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="929" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A929" t="s">
         <v>1090</v>
       </c>
@@ -18493,7 +18538,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="930" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="930" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A930" t="s">
         <v>1090</v>
       </c>
@@ -18507,7 +18552,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="931" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="931" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A931" t="s">
         <v>1090</v>
       </c>
@@ -18521,7 +18566,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="932" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="932" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A932" t="s">
         <v>1090</v>
       </c>
@@ -18535,7 +18580,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="933" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="933" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A933" t="s">
         <v>1090</v>
       </c>
@@ -18549,7 +18594,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="934" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="934" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A934" t="s">
         <v>1090</v>
       </c>
@@ -18563,7 +18608,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="935" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="935" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A935" t="s">
         <v>1090</v>
       </c>
@@ -18577,7 +18622,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="936" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="936" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A936" t="s">
         <v>1090</v>
       </c>
@@ -18591,7 +18636,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="937" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="937" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A937" t="s">
         <v>1090</v>
       </c>
@@ -18605,7 +18650,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="938" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="938" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A938" t="s">
         <v>1090</v>
       </c>
@@ -18619,7 +18664,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="939" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="939" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A939" t="s">
         <v>1090</v>
       </c>
@@ -18633,7 +18678,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="940" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="940" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A940" t="s">
         <v>1090</v>
       </c>
@@ -18647,7 +18692,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="941" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="941" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A941" t="s">
         <v>1090</v>
       </c>
@@ -18661,7 +18706,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="942" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="942" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A942" t="s">
         <v>1090</v>
       </c>
@@ -18675,7 +18720,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="943" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="943" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A943" t="s">
         <v>1090</v>
       </c>
@@ -18689,7 +18734,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="944" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="944" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A944" t="s">
         <v>1090</v>
       </c>
@@ -18703,7 +18748,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="945" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="945" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A945" t="s">
         <v>1090</v>
       </c>
@@ -18717,7 +18762,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="946" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="946" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A946" t="s">
         <v>1090</v>
       </c>
@@ -18731,7 +18776,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="947" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="947" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A947" t="s">
         <v>1090</v>
       </c>
@@ -18745,7 +18790,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="948" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="948" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A948" t="s">
         <v>1090</v>
       </c>
@@ -18759,7 +18804,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="949" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="949" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A949" t="s">
         <v>1090</v>
       </c>
@@ -18773,7 +18818,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="950" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="950" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A950" t="s">
         <v>1090</v>
       </c>
@@ -18787,7 +18832,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="951" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="951" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A951" t="s">
         <v>1090</v>
       </c>
@@ -18801,7 +18846,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="952" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="952" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A952" t="s">
         <v>1090</v>
       </c>
@@ -18815,7 +18860,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="953" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="953" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A953" t="s">
         <v>1090</v>
       </c>
@@ -18829,7 +18874,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="954" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="954" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A954" t="s">
         <v>1090</v>
       </c>
@@ -18843,7 +18888,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="955" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="955" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A955" t="s">
         <v>1090</v>
       </c>
@@ -18851,7 +18896,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="956" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="956" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A956" t="s">
         <v>1090</v>
       </c>
@@ -18865,7 +18910,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="957" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="957" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A957" t="s">
         <v>1090</v>
       </c>
@@ -18879,7 +18924,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="958" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="958" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A958" t="s">
         <v>1090</v>
       </c>
@@ -18893,7 +18938,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="959" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="959" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A959" t="s">
         <v>1090</v>
       </c>
@@ -18907,7 +18952,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="960" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="960" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A960" t="s">
         <v>1090</v>
       </c>
@@ -18921,7 +18966,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="961" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="961" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A961" t="s">
         <v>1090</v>
       </c>
@@ -18935,7 +18980,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="962" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="962" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A962" t="s">
         <v>1090</v>
       </c>
@@ -18949,7 +18994,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="963" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="963" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A963" t="s">
         <v>1090</v>
       </c>
@@ -18963,7 +19008,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="964" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="964" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A964" t="s">
         <v>1090</v>
       </c>
@@ -18977,7 +19022,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="965" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A965" t="s">
         <v>1090</v>
       </c>
@@ -18991,7 +19036,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="966" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="966" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A966" t="s">
         <v>1090</v>
       </c>
@@ -19005,7 +19050,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="967" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="967" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A967" t="s">
         <v>1090</v>
       </c>
@@ -19021,7 +19066,7 @@
     </row>
     <row r="968" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A968" t="s">
-        <v>1298</v>
+        <v>1090</v>
       </c>
       <c r="B968">
         <v>2</v>
@@ -19033,21 +19078,21 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="969" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="969" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A969" t="s">
         <v>1298</v>
       </c>
       <c r="B969">
         <v>2</v>
       </c>
-      <c r="C969">
-        <v>12</v>
+      <c r="C969" t="s">
+        <v>1360</v>
       </c>
       <c r="D969" s="6" t="s">
         <v>1300</v>
       </c>
     </row>
-    <row r="970" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="970" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A970" t="s">
         <v>1298</v>
       </c>
@@ -19061,7 +19106,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="971" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="971" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A971" t="s">
         <v>1298</v>
       </c>
@@ -19075,7 +19120,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="972" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="972" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A972" t="s">
         <v>1298</v>
       </c>
@@ -19089,7 +19134,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="973" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="973" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A973" t="s">
         <v>1298</v>
       </c>
@@ -19103,7 +19148,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="974" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="974" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A974" t="s">
         <v>1298</v>
       </c>
@@ -19117,7 +19162,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="975" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="975" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A975" t="s">
         <v>1298</v>
       </c>
@@ -19131,35 +19176,32 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="976" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A976" t="s">
-        <v>1298</v>
-      </c>
+    <row r="976" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B976">
         <v>3</v>
       </c>
-      <c r="C976" t="s">
-        <v>1310</v>
+      <c r="C976">
+        <v>0</v>
       </c>
       <c r="D976" s="6" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="977" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A977" t="s">
         <v>1298</v>
       </c>
       <c r="B977">
         <v>3</v>
       </c>
-      <c r="C977">
-        <v>17</v>
+      <c r="C977" t="s">
+        <v>1310</v>
       </c>
       <c r="D977" s="6" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="978" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A978" t="s">
         <v>1298</v>
       </c>
@@ -19170,24 +19212,24 @@
         <v>17</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="979" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A979" t="s">
         <v>1298</v>
       </c>
       <c r="B979">
-        <v>4</v>
-      </c>
-      <c r="C979" t="s">
-        <v>1315</v>
+        <v>3</v>
+      </c>
+      <c r="C979">
+        <v>17</v>
       </c>
       <c r="D979" s="6" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="980" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A980" t="s">
         <v>1298</v>
       </c>
@@ -19198,10 +19240,10 @@
         <v>1315</v>
       </c>
       <c r="D980" s="6" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="981" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A981" t="s">
         <v>1298</v>
       </c>
@@ -19209,41 +19251,41 @@
         <v>4</v>
       </c>
       <c r="C981" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D981" s="6" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="982" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A982" t="s">
         <v>1298</v>
       </c>
       <c r="B982">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C982" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="D982" s="6" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="983" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A983" t="s">
         <v>1298</v>
       </c>
       <c r="B983">
         <v>5</v>
       </c>
-      <c r="C983">
-        <v>12</v>
+      <c r="C983" t="s">
+        <v>1365</v>
       </c>
       <c r="D983" s="6" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="984" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A984" t="s">
         <v>1298</v>
       </c>
@@ -19251,41 +19293,41 @@
         <v>5</v>
       </c>
       <c r="C984">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D984" s="6" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="985" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A985" t="s">
         <v>1298</v>
       </c>
       <c r="B985">
-        <v>6</v>
-      </c>
-      <c r="C985" t="s">
-        <v>1323</v>
+        <v>5</v>
+      </c>
+      <c r="C985">
+        <v>13</v>
       </c>
       <c r="D985" s="6" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="986" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A986" t="s">
         <v>1298</v>
       </c>
       <c r="B986">
         <v>6</v>
       </c>
-      <c r="C986">
-        <v>17</v>
+      <c r="C986" t="s">
+        <v>1364</v>
       </c>
       <c r="D986" s="6" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="987" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A987" t="s">
         <v>1298</v>
       </c>
@@ -19296,10 +19338,10 @@
         <v>17</v>
       </c>
       <c r="D987" s="6" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="988" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A988" t="s">
         <v>1298</v>
       </c>
@@ -19310,24 +19352,24 @@
         <v>17</v>
       </c>
       <c r="D988" s="6" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="989" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A989" t="s">
         <v>1298</v>
       </c>
       <c r="B989">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C989">
         <v>17</v>
       </c>
       <c r="D989" s="6" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="990" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A990" t="s">
         <v>1298</v>
       </c>
@@ -19335,41 +19377,41 @@
         <v>7</v>
       </c>
       <c r="C990" t="s">
-        <v>1329</v>
+        <v>591</v>
       </c>
       <c r="D990" s="6" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="991" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A991" t="s">
         <v>1298</v>
       </c>
       <c r="B991">
         <v>7</v>
       </c>
-      <c r="C991">
-        <v>17</v>
+      <c r="C991" t="s">
+        <v>1327</v>
       </c>
       <c r="D991" s="6" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="992" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A992" t="s">
         <v>1298</v>
       </c>
       <c r="B992">
         <v>7</v>
       </c>
-      <c r="C992" t="s">
-        <v>1332</v>
+      <c r="C992">
+        <v>17</v>
       </c>
       <c r="D992" s="6" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="993" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A993" t="s">
         <v>1298</v>
       </c>
@@ -19377,83 +19419,83 @@
         <v>7</v>
       </c>
       <c r="C993">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D993" s="6" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="994" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A994" t="s">
         <v>1298</v>
       </c>
       <c r="B994">
         <v>7</v>
       </c>
-      <c r="C994">
-        <v>17</v>
+      <c r="C994" t="s">
+        <v>1330</v>
       </c>
       <c r="D994" s="6" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="995" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A995" t="s">
         <v>1298</v>
       </c>
       <c r="B995">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C995">
         <v>17</v>
       </c>
       <c r="D995" s="6" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="996" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A996" t="s">
         <v>1298</v>
       </c>
       <c r="B996">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C996">
         <v>17</v>
       </c>
       <c r="D996" s="6" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="997" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A997" t="s">
         <v>1298</v>
       </c>
       <c r="B997">
         <v>8</v>
       </c>
-      <c r="C997" t="s">
-        <v>1338</v>
+      <c r="C997">
+        <v>17</v>
       </c>
       <c r="D997" s="6" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="998" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A998" t="s">
         <v>1298</v>
       </c>
       <c r="B998">
         <v>8</v>
       </c>
-      <c r="C998" t="s">
-        <v>84</v>
+      <c r="C998">
+        <v>17</v>
       </c>
       <c r="D998" s="6" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="999" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A999" t="s">
         <v>1298</v>
       </c>
@@ -19461,13 +19503,13 @@
         <v>8</v>
       </c>
       <c r="C999" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="D999" s="6" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="1000" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1000" t="s">
         <v>1298</v>
       </c>
@@ -19475,181 +19517,181 @@
         <v>8</v>
       </c>
       <c r="C1000" t="s">
-        <v>1343</v>
+        <v>84</v>
       </c>
       <c r="D1000" s="6" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1001" t="s">
         <v>1298</v>
       </c>
       <c r="B1001">
-        <v>9</v>
-      </c>
-      <c r="C1001">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="C1001" t="s">
+        <v>1361</v>
       </c>
       <c r="D1001" s="6" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1002" t="s">
         <v>1298</v>
       </c>
       <c r="B1002">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1002" t="s">
-        <v>824</v>
+        <v>1339</v>
       </c>
       <c r="D1002" s="6" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1003" t="s">
         <v>1298</v>
       </c>
       <c r="B1003">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1003" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="D1003" s="6" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="1004" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1004" t="s">
         <v>1298</v>
       </c>
       <c r="B1004">
         <v>9</v>
       </c>
-      <c r="C1004" t="s">
-        <v>1349</v>
+      <c r="C1004">
+        <v>17</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1005" t="s">
         <v>1298</v>
       </c>
       <c r="B1005">
         <v>9</v>
       </c>
-      <c r="C1005">
-        <v>17</v>
+      <c r="C1005" t="s">
+        <v>824</v>
       </c>
       <c r="D1005" s="6" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="1006" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1006" t="s">
         <v>1298</v>
       </c>
       <c r="B1006">
         <v>9</v>
       </c>
-      <c r="C1006">
-        <v>17</v>
+      <c r="C1006" t="s">
+        <v>1345</v>
       </c>
       <c r="D1006" s="6" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1007" t="s">
         <v>1298</v>
       </c>
       <c r="B1007">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1007" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="D1007" s="6" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="1008" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1008" t="s">
         <v>1298</v>
       </c>
       <c r="B1008">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1008">
         <v>17</v>
       </c>
       <c r="D1008" s="6" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="1009" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1009" t="s">
         <v>1298</v>
       </c>
       <c r="B1009">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1009">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D1009" s="6" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="1010" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1010" t="s">
         <v>1298</v>
       </c>
       <c r="B1010">
-        <v>11</v>
-      </c>
-      <c r="C1010">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>1362</v>
       </c>
       <c r="D1010" s="6" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="1011" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1011" t="s">
         <v>1298</v>
       </c>
       <c r="B1011">
-        <v>11</v>
-      </c>
-      <c r="C1011">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="C1011" t="s">
+        <v>591</v>
       </c>
       <c r="D1011" s="6" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="1012" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1012" t="s">
         <v>1298</v>
       </c>
       <c r="B1012">
-        <v>11</v>
-      </c>
-      <c r="C1012" t="s">
-        <v>585</v>
+        <v>10</v>
+      </c>
+      <c r="C1012">
+        <v>0</v>
       </c>
       <c r="D1012" s="6" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="1013" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1013" t="s">
         <v>1298</v>
       </c>
@@ -19657,13 +19699,13 @@
         <v>11</v>
       </c>
       <c r="C1013">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D1013" s="6" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="1014" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1014" t="s">
         <v>1298</v>
       </c>
@@ -19674,28 +19716,70 @@
         <v>17</v>
       </c>
       <c r="D1014" s="6" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="1015" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1015" t="s">
         <v>1298</v>
       </c>
       <c r="B1015">
         <v>11</v>
       </c>
-      <c r="C1015">
+      <c r="C1015" t="s">
+        <v>585</v>
+      </c>
+      <c r="D1015" s="6" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1016" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1016">
+        <v>11</v>
+      </c>
+      <c r="C1016">
         <v>17</v>
       </c>
-      <c r="D1015" s="6" t="s">
-        <v>1361</v>
+      <c r="D1016" s="6" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1017" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1017">
+        <v>11</v>
+      </c>
+      <c r="C1017" t="s">
+        <v>591</v>
+      </c>
+      <c r="D1017" s="6" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A1018" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1018">
+        <v>11</v>
+      </c>
+      <c r="C1018">
+        <v>17</v>
+      </c>
+      <c r="D1018" s="6" t="s">
+        <v>1358</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1015" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
+  <autoFilter ref="A1:I1018" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
     <filterColumn colId="0">
       <filters>
-        <filter val="OCDE_2024"/>
+        <filter val="G20_2024"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
+++ b/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/cpaltat_upv_edu_es/Documents/TFM/Data/Annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3189" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F8F6DB7-997A-4569-82AF-14E9F6D56E2B}"/>
+  <xr:revisionPtr revIDLastSave="3197" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E94D9DA-2909-44A8-BA9A-561C743192C5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{49184B03-C425-4292-8179-3E0C1E060977}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="1367">
   <si>
     <t>Page</t>
   </si>
@@ -4964,6 +4964,9 @@
   </si>
   <si>
     <t>OCDE_2024_</t>
+  </si>
+  <si>
+    <t>10, 1, 8</t>
   </si>
 </sst>
 </file>
@@ -5541,6 +5544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I1018"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5569,7 +5573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>447</v>
       </c>
@@ -5583,7 +5587,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>447</v>
       </c>
@@ -5597,7 +5601,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>447</v>
       </c>
@@ -5611,7 +5615,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>447</v>
       </c>
@@ -5625,7 +5629,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>447</v>
       </c>
@@ -5639,7 +5643,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>447</v>
       </c>
@@ -5681,7 +5685,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>447</v>
       </c>
@@ -5695,7 +5699,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>447</v>
       </c>
@@ -5709,7 +5713,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>447</v>
       </c>
@@ -5723,7 +5727,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>447</v>
       </c>
@@ -5737,7 +5741,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>447</v>
       </c>
@@ -5751,7 +5755,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>447</v>
       </c>
@@ -5765,7 +5769,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>447</v>
       </c>
@@ -5779,7 +5783,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>447</v>
       </c>
@@ -5793,7 +5797,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>447</v>
       </c>
@@ -5877,7 +5881,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>447</v>
       </c>
@@ -5891,7 +5895,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>447</v>
       </c>
@@ -5905,7 +5909,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>447</v>
       </c>
@@ -5919,7 +5923,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>447</v>
       </c>
@@ -5933,7 +5937,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>447</v>
       </c>
@@ -5947,7 +5951,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>447</v>
       </c>
@@ -5961,7 +5965,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>447</v>
       </c>
@@ -5975,7 +5979,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>447</v>
       </c>
@@ -5989,7 +5993,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>447</v>
       </c>
@@ -6003,7 +6007,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>447</v>
       </c>
@@ -6017,7 +6021,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>447</v>
       </c>
@@ -6031,7 +6035,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>447</v>
       </c>
@@ -6045,7 +6049,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>447</v>
       </c>
@@ -6073,7 +6077,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>447</v>
       </c>
@@ -6087,7 +6091,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>447</v>
       </c>
@@ -6101,7 +6105,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>447</v>
       </c>
@@ -6112,7 +6116,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>447</v>
       </c>
@@ -6123,7 +6127,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>447</v>
       </c>
@@ -6134,7 +6138,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>447</v>
       </c>
@@ -6148,7 +6152,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>447</v>
       </c>
@@ -6162,7 +6166,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>447</v>
       </c>
@@ -6176,7 +6180,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>447</v>
       </c>
@@ -6190,7 +6194,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>447</v>
       </c>
@@ -6204,7 +6208,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>447</v>
       </c>
@@ -6218,7 +6222,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>447</v>
       </c>
@@ -6232,7 +6236,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>447</v>
       </c>
@@ -6246,7 +6250,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>447</v>
       </c>
@@ -6260,7 +6264,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>447</v>
       </c>
@@ -6274,7 +6278,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>447</v>
       </c>
@@ -6288,7 +6292,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>447</v>
       </c>
@@ -6302,7 +6306,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>447</v>
       </c>
@@ -6316,7 +6320,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>447</v>
       </c>
@@ -6330,7 +6334,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>447</v>
       </c>
@@ -6344,7 +6348,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>447</v>
       </c>
@@ -6358,7 +6362,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>447</v>
       </c>
@@ -6372,7 +6376,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>447</v>
       </c>
@@ -6386,7 +6390,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>447</v>
       </c>
@@ -6400,7 +6404,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>447</v>
       </c>
@@ -6414,7 +6418,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>447</v>
       </c>
@@ -6428,7 +6432,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>447</v>
       </c>
@@ -6442,7 +6446,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>447</v>
       </c>
@@ -6456,7 +6460,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>447</v>
       </c>
@@ -6470,7 +6474,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>447</v>
       </c>
@@ -6484,7 +6488,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>447</v>
       </c>
@@ -6498,7 +6502,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>447</v>
       </c>
@@ -6554,7 +6558,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>447</v>
       </c>
@@ -6568,7 +6572,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>447</v>
       </c>
@@ -6582,7 +6586,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>447</v>
       </c>
@@ -6610,7 +6614,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>447</v>
       </c>
@@ -6624,7 +6628,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>447</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>447</v>
       </c>
@@ -6666,7 +6670,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>447</v>
       </c>
@@ -6680,7 +6684,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>447</v>
       </c>
@@ -6694,7 +6698,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>447</v>
       </c>
@@ -6708,7 +6712,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>447</v>
       </c>
@@ -6722,7 +6726,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>447</v>
       </c>
@@ -6750,7 +6754,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>447</v>
       </c>
@@ -6764,7 +6768,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>447</v>
       </c>
@@ -6778,7 +6782,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>447</v>
       </c>
@@ -6792,7 +6796,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>447</v>
       </c>
@@ -6806,7 +6810,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>447</v>
       </c>
@@ -6820,7 +6824,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>447</v>
       </c>
@@ -6834,7 +6838,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>447</v>
       </c>
@@ -6848,7 +6852,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>447</v>
       </c>
@@ -6862,7 +6866,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>447</v>
       </c>
@@ -6876,7 +6880,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>447</v>
       </c>
@@ -6890,7 +6894,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>447</v>
       </c>
@@ -6918,7 +6922,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>447</v>
       </c>
@@ -6932,7 +6936,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>447</v>
       </c>
@@ -6946,7 +6950,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>447</v>
       </c>
@@ -6960,7 +6964,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>447</v>
       </c>
@@ -6974,7 +6978,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>447</v>
       </c>
@@ -6988,7 +6992,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="104" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>447</v>
       </c>
@@ -7002,7 +7006,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>447</v>
       </c>
@@ -7044,7 +7048,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>447</v>
       </c>
@@ -7058,7 +7062,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>447</v>
       </c>
@@ -7072,7 +7076,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>447</v>
       </c>
@@ -7086,7 +7090,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>447</v>
       </c>
@@ -7100,7 +7104,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>447</v>
       </c>
@@ -7128,7 +7132,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>447</v>
       </c>
@@ -7156,7 +7160,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>447</v>
       </c>
@@ -7170,7 +7174,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>447</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>447</v>
       </c>
@@ -7198,7 +7202,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>447</v>
       </c>
@@ -7212,7 +7216,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>447</v>
       </c>
@@ -7226,7 +7230,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:4" ht="142.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>447</v>
       </c>
@@ -7240,7 +7244,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>447</v>
       </c>
@@ -7254,7 +7258,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="123" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>447</v>
       </c>
@@ -7268,7 +7272,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>447</v>
       </c>
@@ -7282,7 +7286,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>447</v>
       </c>
@@ -7296,7 +7300,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>447</v>
       </c>
@@ -7310,7 +7314,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>447</v>
       </c>
@@ -7324,7 +7328,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>447</v>
       </c>
@@ -7338,7 +7342,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>447</v>
       </c>
@@ -7366,7 +7370,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>447</v>
       </c>
@@ -7380,7 +7384,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>447</v>
       </c>
@@ -7394,7 +7398,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>447</v>
       </c>
@@ -7408,7 +7412,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>447</v>
       </c>
@@ -7422,7 +7426,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>447</v>
       </c>
@@ -7436,7 +7440,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>447</v>
       </c>
@@ -7450,7 +7454,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>447</v>
       </c>
@@ -7464,7 +7468,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>447</v>
       </c>
@@ -7478,7 +7482,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>447</v>
       </c>
@@ -7492,7 +7496,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>447</v>
       </c>
@@ -7506,7 +7510,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>447</v>
       </c>
@@ -7520,7 +7524,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>447</v>
       </c>
@@ -7534,7 +7538,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>447</v>
       </c>
@@ -7548,7 +7552,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>447</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>447</v>
       </c>
@@ -7576,7 +7580,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>447</v>
       </c>
@@ -7590,7 +7594,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>447</v>
       </c>
@@ -7604,7 +7608,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>447</v>
       </c>
@@ -7632,7 +7636,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>447</v>
       </c>
@@ -7646,7 +7650,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>447</v>
       </c>
@@ -7660,7 +7664,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>447</v>
       </c>
@@ -7688,7 +7692,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>447</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>447</v>
       </c>
@@ -7716,7 +7720,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>447</v>
       </c>
@@ -7744,7 +7748,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>447</v>
       </c>
@@ -7758,7 +7762,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>447</v>
       </c>
@@ -7772,7 +7776,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>447</v>
       </c>
@@ -7786,7 +7790,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>447</v>
       </c>
@@ -7800,7 +7804,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>447</v>
       </c>
@@ -7814,7 +7818,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>447</v>
       </c>
@@ -7828,7 +7832,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>447</v>
       </c>
@@ -7842,7 +7846,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>447</v>
       </c>
@@ -7856,7 +7860,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>447</v>
       </c>
@@ -7870,7 +7874,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>447</v>
       </c>
@@ -7884,7 +7888,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="168" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>447</v>
       </c>
@@ -7898,7 +7902,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="169" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>447</v>
       </c>
@@ -7912,7 +7916,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="170" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>447</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>447</v>
       </c>
@@ -7940,7 +7944,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>447</v>
       </c>
@@ -7954,7 +7958,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>447</v>
       </c>
@@ -7968,7 +7972,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>447</v>
       </c>
@@ -7982,7 +7986,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>447</v>
       </c>
@@ -8010,7 +8014,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="177" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>447</v>
       </c>
@@ -8038,7 +8042,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>447</v>
       </c>
@@ -8049,7 +8053,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>447</v>
       </c>
@@ -8063,7 +8067,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>447</v>
       </c>
@@ -8077,7 +8081,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>447</v>
       </c>
@@ -8091,7 +8095,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>447</v>
       </c>
@@ -8105,7 +8109,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>447</v>
       </c>
@@ -8119,7 +8123,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>447</v>
       </c>
@@ -8133,7 +8137,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>447</v>
       </c>
@@ -8147,7 +8151,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>447</v>
       </c>
@@ -8161,7 +8165,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>447</v>
       </c>
@@ -8175,7 +8179,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>447</v>
       </c>
@@ -8189,7 +8193,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>447</v>
       </c>
@@ -8203,7 +8207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="191" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>447</v>
       </c>
@@ -8217,7 +8221,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="192" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>447</v>
       </c>
@@ -8231,7 +8235,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="193" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>447</v>
       </c>
@@ -8245,7 +8249,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>447</v>
       </c>
@@ -8259,7 +8263,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>447</v>
       </c>
@@ -8273,7 +8277,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>447</v>
       </c>
@@ -8301,7 +8305,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>447</v>
       </c>
@@ -8315,7 +8319,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>447</v>
       </c>
@@ -8329,7 +8333,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="200" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>447</v>
       </c>
@@ -8343,7 +8347,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="201" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>447</v>
       </c>
@@ -8357,7 +8361,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="202" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A202" t="s">
         <v>447</v>
       </c>
@@ -8385,7 +8389,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="204" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A204" t="s">
         <v>447</v>
       </c>
@@ -8399,7 +8403,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A205" t="s">
         <v>447</v>
       </c>
@@ -8413,7 +8417,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A206" t="s">
         <v>447</v>
       </c>
@@ -8427,7 +8431,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="207" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A207" t="s">
         <v>447</v>
       </c>
@@ -8441,7 +8445,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="208" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A208" t="s">
         <v>447</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="209" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A209" t="s">
         <v>447</v>
       </c>
@@ -8469,7 +8473,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="210" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A210" t="s">
         <v>447</v>
       </c>
@@ -8483,7 +8487,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="211" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A211" t="s">
         <v>447</v>
       </c>
@@ -8497,7 +8501,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>447</v>
       </c>
@@ -8511,7 +8515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>447</v>
       </c>
@@ -8525,7 +8529,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="214" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A214" t="s">
         <v>447</v>
       </c>
@@ -8539,7 +8543,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="215" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A215" t="s">
         <v>447</v>
       </c>
@@ -8567,7 +8571,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A217" t="s">
         <v>447</v>
       </c>
@@ -8581,7 +8585,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A218" t="s">
         <v>447</v>
       </c>
@@ -8609,7 +8613,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>447</v>
       </c>
@@ -8623,7 +8627,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>447</v>
       </c>
@@ -8637,7 +8641,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>447</v>
       </c>
@@ -8651,7 +8655,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>447</v>
       </c>
@@ -8665,7 +8669,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="224" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>447</v>
       </c>
@@ -8679,7 +8683,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="225" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>447</v>
       </c>
@@ -8693,7 +8697,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>447</v>
       </c>
@@ -8707,7 +8711,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="227" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A227" t="s">
         <v>447</v>
       </c>
@@ -8721,7 +8725,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="228" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
         <v>447</v>
       </c>
@@ -8735,7 +8739,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="229" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A229" t="s">
         <v>447</v>
       </c>
@@ -8749,7 +8753,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="230" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A230" t="s">
         <v>447</v>
       </c>
@@ -8763,7 +8767,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="231" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A231" t="s">
         <v>447</v>
       </c>
@@ -8791,7 +8795,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="233" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A233" t="s">
         <v>447</v>
       </c>
@@ -8805,7 +8809,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="234" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A234" t="s">
         <v>447</v>
       </c>
@@ -8819,7 +8823,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
         <v>447</v>
       </c>
@@ -8833,7 +8837,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="236" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A236" t="s">
         <v>447</v>
       </c>
@@ -8847,7 +8851,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="237" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A237" t="s">
         <v>449</v>
       </c>
@@ -8861,7 +8865,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="238" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A238" t="s">
         <v>449</v>
       </c>
@@ -8875,7 +8879,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="239" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A239" t="s">
         <v>449</v>
       </c>
@@ -8889,7 +8893,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A240" t="s">
         <v>449</v>
       </c>
@@ -8903,7 +8907,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A241" t="s">
         <v>449</v>
       </c>
@@ -8917,7 +8921,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="242" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
         <v>449</v>
       </c>
@@ -8931,7 +8935,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A243" t="s">
         <v>449</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A244" t="s">
         <v>449</v>
       </c>
@@ -8959,7 +8963,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="245" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A245" t="s">
         <v>449</v>
       </c>
@@ -8973,7 +8977,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="246" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A246" t="s">
         <v>449</v>
       </c>
@@ -8987,7 +8991,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A247" t="s">
         <v>449</v>
       </c>
@@ -9015,7 +9019,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
         <v>449</v>
       </c>
@@ -9146,7 +9150,7 @@
         <v>30</v>
       </c>
       <c r="C258" t="s">
-        <v>182</v>
+        <v>1366</v>
       </c>
       <c r="D258" s="6" t="s">
         <v>386</v>
@@ -9334,7 +9338,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="272" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A272" t="s">
         <v>449</v>
       </c>
@@ -9348,7 +9352,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="273" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A273" t="s">
         <v>449</v>
       </c>
@@ -9362,7 +9366,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="274" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A274" t="s">
         <v>449</v>
       </c>
@@ -9376,7 +9380,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="275" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A275" t="s">
         <v>449</v>
       </c>
@@ -9390,7 +9394,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="276" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A276" t="s">
         <v>449</v>
       </c>
@@ -9404,7 +9408,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="277" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
         <v>449</v>
       </c>
@@ -9418,7 +9422,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A278" t="s">
         <v>449</v>
       </c>
@@ -9432,7 +9436,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A279" t="s">
         <v>449</v>
       </c>
@@ -9446,7 +9450,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A280" t="s">
         <v>449</v>
       </c>
@@ -9460,7 +9464,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="281" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A281" t="s">
         <v>449</v>
       </c>
@@ -9474,7 +9478,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="282" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A282" t="s">
         <v>449</v>
       </c>
@@ -9488,7 +9492,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A283" t="s">
         <v>449</v>
       </c>
@@ -9502,7 +9506,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="284" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
         <v>449</v>
       </c>
@@ -9516,7 +9520,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="285" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A285" t="s">
         <v>449</v>
       </c>
@@ -9530,7 +9534,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A286" t="s">
         <v>449</v>
       </c>
@@ -9544,7 +9548,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="287" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A287" t="s">
         <v>449</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="288" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A288" t="s">
         <v>449</v>
       </c>
@@ -9572,7 +9576,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="289" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A289" t="s">
         <v>449</v>
       </c>
@@ -9586,7 +9590,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="290" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A290" t="s">
         <v>449</v>
       </c>
@@ -9600,7 +9604,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
         <v>449</v>
       </c>
@@ -9642,7 +9646,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="294" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A294" t="s">
         <v>449</v>
       </c>
@@ -9656,7 +9660,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A295" t="s">
         <v>449</v>
       </c>
@@ -9670,7 +9674,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="296" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A296" t="s">
         <v>449</v>
       </c>
@@ -9684,7 +9688,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="297" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A297" t="s">
         <v>449</v>
       </c>
@@ -9712,7 +9716,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
         <v>449</v>
       </c>
@@ -9726,7 +9730,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A300" t="s">
         <v>449</v>
       </c>
@@ -9740,7 +9744,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A301" t="s">
         <v>449</v>
       </c>
@@ -9768,7 +9772,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="303" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A303" t="s">
         <v>449</v>
       </c>
@@ -9782,7 +9786,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" t="s">
         <v>449</v>
       </c>
@@ -9810,7 +9814,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A306" t="s">
         <v>449</v>
       </c>
@@ -9824,7 +9828,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>449</v>
       </c>
@@ -9838,7 +9842,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>449</v>
       </c>
@@ -9852,7 +9856,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>449</v>
       </c>
@@ -9866,7 +9870,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A310" t="s">
         <v>449</v>
       </c>
@@ -9894,7 +9898,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A312" t="s">
         <v>449</v>
       </c>
@@ -9908,7 +9912,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="313" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A313" t="s">
         <v>449</v>
       </c>
@@ -9922,7 +9926,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A314" t="s">
         <v>449</v>
       </c>
@@ -9936,7 +9940,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
         <v>449</v>
       </c>
@@ -9950,7 +9954,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>449</v>
       </c>
@@ -9964,7 +9968,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A317" t="s">
         <v>449</v>
       </c>
@@ -9978,7 +9982,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A318" t="s">
         <v>449</v>
       </c>
@@ -9992,7 +9996,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>449</v>
       </c>
@@ -10006,7 +10010,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>449</v>
       </c>
@@ -10020,7 +10024,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A321" t="s">
         <v>449</v>
       </c>
@@ -10034,7 +10038,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322" t="s">
         <v>449</v>
       </c>
@@ -10048,7 +10052,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
         <v>449</v>
       </c>
@@ -10062,7 +10066,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A324" t="s">
         <v>449</v>
       </c>
@@ -10076,7 +10080,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>449</v>
       </c>
@@ -10090,7 +10094,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A326" t="s">
         <v>449</v>
       </c>
@@ -10104,7 +10108,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A327" t="s">
         <v>449</v>
       </c>
@@ -10118,7 +10122,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A328" t="s">
         <v>449</v>
       </c>
@@ -10132,7 +10136,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A329" t="s">
         <v>449</v>
       </c>
@@ -10146,7 +10150,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A330" t="s">
         <v>449</v>
       </c>
@@ -10160,7 +10164,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>449</v>
       </c>
@@ -10174,7 +10178,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A332" t="s">
         <v>449</v>
       </c>
@@ -10188,7 +10192,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="333" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A333" t="s">
         <v>449</v>
       </c>
@@ -10202,7 +10206,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="334" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A334" t="s">
         <v>449</v>
       </c>
@@ -10216,7 +10220,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A335" t="s">
         <v>449</v>
       </c>
@@ -10244,7 +10248,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A337" t="s">
         <v>449</v>
       </c>
@@ -10258,7 +10262,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A338" t="s">
         <v>449</v>
       </c>
@@ -10272,7 +10276,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>449</v>
       </c>
@@ -10286,7 +10290,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="340" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A340" t="s">
         <v>449</v>
       </c>
@@ -10300,7 +10304,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>449</v>
       </c>
@@ -10314,7 +10318,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>449</v>
       </c>
@@ -10328,7 +10332,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>449</v>
       </c>
@@ -10342,7 +10346,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>449</v>
       </c>
@@ -10356,7 +10360,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A345" t="s">
         <v>449</v>
       </c>
@@ -10370,7 +10374,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A346" t="s">
         <v>449</v>
       </c>
@@ -10384,7 +10388,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="347" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
         <v>449</v>
       </c>
@@ -10398,7 +10402,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>449</v>
       </c>
@@ -10412,7 +10416,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A349" t="s">
         <v>449</v>
       </c>
@@ -10426,7 +10430,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>449</v>
       </c>
@@ -10440,7 +10444,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>449</v>
       </c>
@@ -10454,7 +10458,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A352" t="s">
         <v>449</v>
       </c>
@@ -10468,7 +10472,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>449</v>
       </c>
@@ -10482,7 +10486,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>449</v>
       </c>
@@ -10496,7 +10500,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
         <v>449</v>
       </c>
@@ -10510,7 +10514,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A356" t="s">
         <v>449</v>
       </c>
@@ -10524,7 +10528,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>449</v>
       </c>
@@ -10538,7 +10542,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>449</v>
       </c>
@@ -10552,7 +10556,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A359" t="s">
         <v>449</v>
       </c>
@@ -10566,7 +10570,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>449</v>
       </c>
@@ -10580,7 +10584,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A361" t="s">
         <v>449</v>
       </c>
@@ -10594,7 +10598,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A362" t="s">
         <v>449</v>
       </c>
@@ -10608,7 +10612,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
         <v>449</v>
       </c>
@@ -10622,7 +10626,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="364" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A364" t="s">
         <v>449</v>
       </c>
@@ -10636,7 +10640,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>449</v>
       </c>
@@ -10650,7 +10654,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>449</v>
       </c>
@@ -10664,7 +10668,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>449</v>
       </c>
@@ -10678,7 +10682,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>449</v>
       </c>
@@ -10706,7 +10710,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>449</v>
       </c>
@@ -10720,7 +10724,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="371" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
         <v>449</v>
       </c>
@@ -10734,7 +10738,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A372" t="s">
         <v>449</v>
       </c>
@@ -10748,7 +10752,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A373" t="s">
         <v>449</v>
       </c>
@@ -10762,7 +10766,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>449</v>
       </c>
@@ -10776,7 +10780,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="375" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A375" t="s">
         <v>449</v>
       </c>
@@ -10790,7 +10794,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>449</v>
       </c>
@@ -10804,7 +10808,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>449</v>
       </c>
@@ -10818,7 +10822,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>449</v>
       </c>
@@ -10832,7 +10836,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>449</v>
       </c>
@@ -10846,7 +10850,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A380" t="s">
         <v>449</v>
       </c>
@@ -10860,7 +10864,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A381" t="s">
         <v>449</v>
       </c>
@@ -10874,7 +10878,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A382" t="s">
         <v>449</v>
       </c>
@@ -10888,7 +10892,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>449</v>
       </c>
@@ -10902,7 +10906,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>449</v>
       </c>
@@ -10916,7 +10920,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A385" t="s">
         <v>449</v>
       </c>
@@ -10930,7 +10934,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A386" t="s">
         <v>449</v>
       </c>
@@ -10944,7 +10948,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
         <v>449</v>
       </c>
@@ -10958,7 +10962,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A388" t="s">
         <v>449</v>
       </c>
@@ -10972,7 +10976,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="389" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A389" t="s">
         <v>449</v>
       </c>
@@ -10986,7 +10990,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A390" t="s">
         <v>449</v>
       </c>
@@ -11000,7 +11004,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>449</v>
       </c>
@@ -11056,7 +11060,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
         <v>449</v>
       </c>
@@ -11070,7 +11074,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A396" t="s">
         <v>449</v>
       </c>
@@ -11084,7 +11088,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>449</v>
       </c>
@@ -11098,7 +11102,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A398" t="s">
         <v>449</v>
       </c>
@@ -11112,7 +11116,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>449</v>
       </c>
@@ -11126,7 +11130,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A400" t="s">
         <v>449</v>
       </c>
@@ -11140,7 +11144,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A401" t="s">
         <v>449</v>
       </c>
@@ -11154,7 +11158,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="402" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A402" t="s">
         <v>449</v>
       </c>
@@ -11168,7 +11172,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>449</v>
       </c>
@@ -11182,7 +11186,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A404" t="s">
         <v>449</v>
       </c>
@@ -11196,7 +11200,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A405" t="s">
         <v>449</v>
       </c>
@@ -11238,7 +11242,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A408" t="s">
         <v>449</v>
       </c>
@@ -11266,7 +11270,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
         <v>449</v>
       </c>
@@ -11294,7 +11298,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>449</v>
       </c>
@@ -11322,7 +11326,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>449</v>
       </c>
@@ -11336,7 +11340,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A415" t="s">
         <v>449</v>
       </c>
@@ -11350,7 +11354,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="416" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A416" t="s">
         <v>449</v>
       </c>
@@ -11364,7 +11368,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>449</v>
       </c>
@@ -11378,7 +11382,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A418" t="s">
         <v>449</v>
       </c>
@@ -11392,7 +11396,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>449</v>
       </c>
@@ -11420,7 +11424,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>449</v>
       </c>
@@ -11504,7 +11508,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A427" t="s">
         <v>449</v>
       </c>
@@ -11518,7 +11522,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A428" t="s">
         <v>449</v>
       </c>
@@ -11532,7 +11536,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A429" t="s">
         <v>449</v>
       </c>
@@ -11546,7 +11550,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A430" t="s">
         <v>449</v>
       </c>
@@ -11560,7 +11564,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A431" t="s">
         <v>449</v>
       </c>
@@ -11588,7 +11592,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A433" t="s">
         <v>449</v>
       </c>
@@ -11644,7 +11648,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A437" t="s">
         <v>449</v>
       </c>
@@ -11756,7 +11760,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A445" t="s">
         <v>449</v>
       </c>
@@ -11812,7 +11816,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>449</v>
       </c>
@@ -11826,7 +11830,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>449</v>
       </c>
@@ -11840,7 +11844,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>449</v>
       </c>
@@ -11854,7 +11858,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>449</v>
       </c>
@@ -11868,7 +11872,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>449</v>
       </c>
@@ -11882,7 +11886,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>449</v>
       </c>
@@ -11910,7 +11914,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>449</v>
       </c>
@@ -11924,7 +11928,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="457" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>449</v>
       </c>
@@ -11952,7 +11956,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>449</v>
       </c>
@@ -11966,7 +11970,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>449</v>
       </c>
@@ -11980,7 +11984,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>449</v>
       </c>
@@ -11994,7 +11998,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>449</v>
       </c>
@@ -12008,7 +12012,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>449</v>
       </c>
@@ -12022,7 +12026,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>449</v>
       </c>
@@ -12036,7 +12040,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="465" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
         <v>449</v>
       </c>
@@ -12050,7 +12054,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
         <v>449</v>
       </c>
@@ -12064,7 +12068,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>449</v>
       </c>
@@ -12106,7 +12110,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>449</v>
       </c>
@@ -12120,7 +12124,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
         <v>449</v>
       </c>
@@ -12134,7 +12138,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>449</v>
       </c>
@@ -12148,7 +12152,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
         <v>449</v>
       </c>
@@ -12162,7 +12166,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
         <v>449</v>
       </c>
@@ -12176,7 +12180,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
         <v>449</v>
       </c>
@@ -12190,7 +12194,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
         <v>449</v>
       </c>
@@ -12204,7 +12208,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
         <v>449</v>
       </c>
@@ -12232,7 +12236,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>449</v>
       </c>
@@ -12246,7 +12250,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
         <v>449</v>
       </c>
@@ -12260,7 +12264,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
         <v>449</v>
       </c>
@@ -12288,7 +12292,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
         <v>449</v>
       </c>
@@ -12302,7 +12306,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="484" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
         <v>449</v>
       </c>
@@ -12316,7 +12320,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
         <v>449</v>
       </c>
@@ -12330,7 +12334,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
         <v>449</v>
       </c>
@@ -12344,7 +12348,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>449</v>
       </c>
@@ -12358,7 +12362,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
         <v>449</v>
       </c>
@@ -12372,7 +12376,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>449</v>
       </c>
@@ -12386,7 +12390,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>449</v>
       </c>
@@ -12400,7 +12404,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>449</v>
       </c>
@@ -12414,7 +12418,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
         <v>449</v>
       </c>
@@ -12428,7 +12432,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
         <v>449</v>
       </c>
@@ -12442,7 +12446,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
         <v>449</v>
       </c>
@@ -12456,7 +12460,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
         <v>449</v>
       </c>
@@ -12470,7 +12474,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
         <v>449</v>
       </c>
@@ -12484,7 +12488,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>449</v>
       </c>
@@ -12498,7 +12502,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
         <v>449</v>
       </c>
@@ -12512,7 +12516,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
         <v>449</v>
       </c>
@@ -12526,7 +12530,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>449</v>
       </c>
@@ -12540,7 +12544,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
         <v>449</v>
       </c>
@@ -12554,7 +12558,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
         <v>449</v>
       </c>
@@ -12568,7 +12572,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
         <v>449</v>
       </c>
@@ -12582,7 +12586,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
         <v>449</v>
       </c>
@@ -12638,7 +12642,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>449</v>
       </c>
@@ -12652,7 +12656,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>449</v>
       </c>
@@ -12680,7 +12684,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A511" t="s">
         <v>449</v>
       </c>
@@ -12722,7 +12726,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>449</v>
       </c>
@@ -12736,7 +12740,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>449</v>
       </c>
@@ -12750,7 +12754,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>449</v>
       </c>
@@ -12764,7 +12768,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>449</v>
       </c>
@@ -12778,7 +12782,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>449</v>
       </c>
@@ -12792,7 +12796,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>449</v>
       </c>
@@ -12834,7 +12838,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>449</v>
       </c>
@@ -12848,7 +12852,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="523" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A523" t="s">
         <v>449</v>
       </c>
@@ -12862,7 +12866,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A524" t="s">
         <v>449</v>
       </c>
@@ -12876,7 +12880,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A525" t="s">
         <v>449</v>
       </c>
@@ -12890,7 +12894,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A526" t="s">
         <v>449</v>
       </c>
@@ -12904,7 +12908,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>449</v>
       </c>
@@ -12918,7 +12922,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A528" t="s">
         <v>449</v>
       </c>
@@ -12932,7 +12936,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>449</v>
       </c>
@@ -12946,7 +12950,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>449</v>
       </c>
@@ -12960,7 +12964,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A531" t="s">
         <v>449</v>
       </c>
@@ -12974,7 +12978,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A532" t="s">
         <v>449</v>
       </c>
@@ -13002,7 +13006,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>449</v>
       </c>
@@ -13058,7 +13062,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A538" t="s">
         <v>449</v>
       </c>
@@ -13072,7 +13076,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A539" t="s">
         <v>449</v>
       </c>
@@ -13086,7 +13090,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A540" t="s">
         <v>449</v>
       </c>
@@ -13100,7 +13104,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A541" t="s">
         <v>449</v>
       </c>
@@ -13114,7 +13118,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A542" t="s">
         <v>449</v>
       </c>
@@ -13128,7 +13132,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>449</v>
       </c>
@@ -13142,7 +13146,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A544" t="s">
         <v>449</v>
       </c>
@@ -13156,7 +13160,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A545" t="s">
         <v>449</v>
       </c>
@@ -13170,7 +13174,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A546" t="s">
         <v>449</v>
       </c>
@@ -13184,7 +13188,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A547" t="s">
         <v>449</v>
       </c>
@@ -13198,7 +13202,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A548" t="s">
         <v>449</v>
       </c>
@@ -13212,7 +13216,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A549" t="s">
         <v>449</v>
       </c>
@@ -13226,7 +13230,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A550" t="s">
         <v>449</v>
       </c>
@@ -13240,7 +13244,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>449</v>
       </c>
@@ -13254,7 +13258,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A552" t="s">
         <v>449</v>
       </c>
@@ -13268,7 +13272,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>449</v>
       </c>
@@ -13282,7 +13286,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>449</v>
       </c>
@@ -13296,7 +13300,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A555" t="s">
         <v>449</v>
       </c>
@@ -13310,7 +13314,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A556" t="s">
         <v>449</v>
       </c>
@@ -13324,7 +13328,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>449</v>
       </c>
@@ -13338,7 +13342,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A558" t="s">
         <v>449</v>
       </c>
@@ -13352,7 +13356,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>449</v>
       </c>
@@ -13366,7 +13370,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A560" t="s">
         <v>449</v>
       </c>
@@ -13380,7 +13384,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A561" t="s">
         <v>449</v>
       </c>
@@ -13394,7 +13398,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A562" t="s">
         <v>449</v>
       </c>
@@ -13408,7 +13412,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A563" t="s">
         <v>449</v>
       </c>
@@ -13422,7 +13426,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A564" t="s">
         <v>449</v>
       </c>
@@ -13436,7 +13440,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>449</v>
       </c>
@@ -13450,7 +13454,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A566" t="s">
         <v>449</v>
       </c>
@@ -13464,7 +13468,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A567" t="s">
         <v>449</v>
       </c>
@@ -13478,7 +13482,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A568" t="s">
         <v>449</v>
       </c>
@@ -13492,7 +13496,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>449</v>
       </c>
@@ -13506,7 +13510,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A570" t="s">
         <v>449</v>
       </c>
@@ -13520,7 +13524,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A571" t="s">
         <v>449</v>
       </c>
@@ -13534,7 +13538,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A572" t="s">
         <v>449</v>
       </c>
@@ -13548,7 +13552,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A573" t="s">
         <v>449</v>
       </c>
@@ -13562,7 +13566,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>449</v>
       </c>
@@ -13576,7 +13580,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>449</v>
       </c>
@@ -13590,7 +13594,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>449</v>
       </c>
@@ -13604,7 +13608,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>449</v>
       </c>
@@ -13618,7 +13622,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A578" t="s">
         <v>449</v>
       </c>
@@ -13632,7 +13636,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>449</v>
       </c>
@@ -13646,7 +13650,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A580" t="s">
         <v>449</v>
       </c>
@@ -13660,7 +13664,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A581" t="s">
         <v>449</v>
       </c>
@@ -13674,7 +13678,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="582" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A582" t="s">
         <v>449</v>
       </c>
@@ -13688,7 +13692,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A583" t="s">
         <v>449</v>
       </c>
@@ -13702,7 +13706,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A584" t="s">
         <v>449</v>
       </c>
@@ -13716,7 +13720,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A585" t="s">
         <v>449</v>
       </c>
@@ -13730,7 +13734,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>449</v>
       </c>
@@ -13744,7 +13748,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>449</v>
       </c>
@@ -13758,7 +13762,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>449</v>
       </c>
@@ -13772,7 +13776,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>449</v>
       </c>
@@ -13786,7 +13790,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>449</v>
       </c>
@@ -13800,7 +13804,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="591" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A591" t="s">
         <v>449</v>
       </c>
@@ -13814,7 +13818,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A592" t="s">
         <v>449</v>
       </c>
@@ -13828,7 +13832,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A593" t="s">
         <v>449</v>
       </c>
@@ -13842,7 +13846,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A594" t="s">
         <v>449</v>
       </c>
@@ -13856,7 +13860,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A595" t="s">
         <v>449</v>
       </c>
@@ -13870,7 +13874,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A596" t="s">
         <v>449</v>
       </c>
@@ -13884,7 +13888,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="597" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A597" t="s">
         <v>449</v>
       </c>
@@ -13898,7 +13902,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>449</v>
       </c>
@@ -13912,7 +13916,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>449</v>
       </c>
@@ -13926,7 +13930,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>449</v>
       </c>
@@ -13940,7 +13944,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A601" t="s">
         <v>449</v>
       </c>
@@ -13968,7 +13972,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>449</v>
       </c>
@@ -13982,7 +13986,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>449</v>
       </c>
@@ -13996,7 +14000,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A605" t="s">
         <v>449</v>
       </c>
@@ -14010,7 +14014,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A606" t="s">
         <v>449</v>
       </c>
@@ -14024,7 +14028,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>449</v>
       </c>
@@ -14038,7 +14042,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>449</v>
       </c>
@@ -14052,7 +14056,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>449</v>
       </c>
@@ -14066,7 +14070,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>449</v>
       </c>
@@ -14080,7 +14084,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>449</v>
       </c>
@@ -14094,7 +14098,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A612" t="s">
         <v>449</v>
       </c>
@@ -14108,7 +14112,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A613" t="s">
         <v>449</v>
       </c>
@@ -14122,7 +14126,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A614" t="s">
         <v>449</v>
       </c>
@@ -14136,7 +14140,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A615" t="s">
         <v>449</v>
       </c>
@@ -14150,7 +14154,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>449</v>
       </c>
@@ -14164,7 +14168,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A617" t="s">
         <v>449</v>
       </c>
@@ -14178,7 +14182,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>449</v>
       </c>
@@ -14192,7 +14196,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A619" t="s">
         <v>449</v>
       </c>
@@ -14206,7 +14210,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A620" t="s">
         <v>449</v>
       </c>
@@ -14234,7 +14238,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A622" t="s">
         <v>449</v>
       </c>
@@ -14248,7 +14252,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A623" t="s">
         <v>449</v>
       </c>
@@ -14262,7 +14266,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="624" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A624" t="s">
         <v>449</v>
       </c>
@@ -14276,7 +14280,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="625" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A625" t="s">
         <v>449</v>
       </c>
@@ -14290,7 +14294,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A626" t="s">
         <v>449</v>
       </c>
@@ -14304,7 +14308,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A627" t="s">
         <v>449</v>
       </c>
@@ -14318,7 +14322,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A628" t="s">
         <v>449</v>
       </c>
@@ -14332,7 +14336,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A629" t="s">
         <v>449</v>
       </c>
@@ -14346,7 +14350,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A630" t="s">
         <v>449</v>
       </c>
@@ -14360,7 +14364,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A631" t="s">
         <v>449</v>
       </c>
@@ -14374,7 +14378,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>449</v>
       </c>
@@ -14388,7 +14392,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>449</v>
       </c>
@@ -14402,7 +14406,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A634" t="s">
         <v>449</v>
       </c>
@@ -14416,7 +14420,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A635" t="s">
         <v>449</v>
       </c>
@@ -14430,7 +14434,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="636" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A636" t="s">
         <v>449</v>
       </c>
@@ -14444,7 +14448,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A637" t="s">
         <v>449</v>
       </c>
@@ -14458,7 +14462,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>449</v>
       </c>
@@ -14472,7 +14476,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A639" t="s">
         <v>449</v>
       </c>
@@ -14486,7 +14490,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>449</v>
       </c>
@@ -14500,7 +14504,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A641" t="s">
         <v>449</v>
       </c>
@@ -14514,7 +14518,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>449</v>
       </c>
@@ -14528,7 +14532,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A643" t="s">
         <v>449</v>
       </c>
@@ -14542,7 +14546,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="644" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A644" t="s">
         <v>449</v>
       </c>
@@ -14556,7 +14560,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A645" t="s">
         <v>449</v>
       </c>
@@ -14570,7 +14574,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A646" t="s">
         <v>449</v>
       </c>
@@ -14584,7 +14588,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A647" t="s">
         <v>449</v>
       </c>
@@ -14598,7 +14602,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A648" t="s">
         <v>449</v>
       </c>
@@ -14612,7 +14616,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>449</v>
       </c>
@@ -14626,7 +14630,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="650" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A650" t="s">
         <v>449</v>
       </c>
@@ -14640,7 +14644,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>449</v>
       </c>
@@ -14654,7 +14658,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="652" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A652" t="s">
         <v>877</v>
       </c>
@@ -14668,7 +14672,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A653" t="s">
         <v>877</v>
       </c>
@@ -14682,7 +14686,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>877</v>
       </c>
@@ -14696,7 +14700,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>877</v>
       </c>
@@ -14710,7 +14714,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A656" t="s">
         <v>877</v>
       </c>
@@ -14724,7 +14728,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A657" t="s">
         <v>877</v>
       </c>
@@ -14738,7 +14742,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A658" t="s">
         <v>877</v>
       </c>
@@ -14752,7 +14756,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A659" t="s">
         <v>877</v>
       </c>
@@ -14766,7 +14770,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A660" t="s">
         <v>877</v>
       </c>
@@ -14780,7 +14784,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="661" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A661" t="s">
         <v>877</v>
       </c>
@@ -14794,7 +14798,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>877</v>
       </c>
@@ -14808,7 +14812,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A663" t="s">
         <v>877</v>
       </c>
@@ -14822,7 +14826,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>877</v>
       </c>
@@ -14836,7 +14840,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A665" t="s">
         <v>877</v>
       </c>
@@ -14864,7 +14868,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A667" t="s">
         <v>877</v>
       </c>
@@ -14920,7 +14924,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A671" t="s">
         <v>877</v>
       </c>
@@ -14934,7 +14938,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>877</v>
       </c>
@@ -14948,7 +14952,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A673" t="s">
         <v>877</v>
       </c>
@@ -14962,7 +14966,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>877</v>
       </c>
@@ -14976,7 +14980,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="675" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A675" t="s">
         <v>877</v>
       </c>
@@ -14990,7 +14994,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A676" t="s">
         <v>877</v>
       </c>
@@ -15018,7 +15022,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>877</v>
       </c>
@@ -15046,7 +15050,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="680" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A680" t="s">
         <v>877</v>
       </c>
@@ -15060,7 +15064,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="681" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A681" t="s">
         <v>877</v>
       </c>
@@ -15074,7 +15078,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="682" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A682" t="s">
         <v>877</v>
       </c>
@@ -15088,7 +15092,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A683" t="s">
         <v>877</v>
       </c>
@@ -15102,7 +15106,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="684" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A684" t="s">
         <v>877</v>
       </c>
@@ -15116,7 +15120,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="685" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A685" t="s">
         <v>877</v>
       </c>
@@ -15130,7 +15134,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="686" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>877</v>
       </c>
@@ -15144,7 +15148,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="687" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>877</v>
       </c>
@@ -15158,7 +15162,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="688" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>877</v>
       </c>
@@ -15186,7 +15190,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A690" t="s">
         <v>877</v>
       </c>
@@ -15200,7 +15204,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>877</v>
       </c>
@@ -15214,7 +15218,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A692" t="s">
         <v>877</v>
       </c>
@@ -15228,7 +15232,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>877</v>
       </c>
@@ -15242,7 +15246,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A694" t="s">
         <v>877</v>
       </c>
@@ -15256,7 +15260,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>877</v>
       </c>
@@ -15270,7 +15274,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A696" t="s">
         <v>877</v>
       </c>
@@ -15284,7 +15288,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A697" t="s">
         <v>877</v>
       </c>
@@ -15298,7 +15302,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="698" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A698" t="s">
         <v>877</v>
       </c>
@@ -15312,7 +15316,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A699" t="s">
         <v>877</v>
       </c>
@@ -15326,7 +15330,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="700" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A700" t="s">
         <v>877</v>
       </c>
@@ -15340,7 +15344,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="701" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A701" t="s">
         <v>877</v>
       </c>
@@ -15354,7 +15358,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="702" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A702" t="s">
         <v>877</v>
       </c>
@@ -15368,7 +15372,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="703" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A703" t="s">
         <v>877</v>
       </c>
@@ -15382,7 +15386,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="704" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>877</v>
       </c>
@@ -15396,7 +15400,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="705" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A705" t="s">
         <v>877</v>
       </c>
@@ -15410,7 +15414,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="706" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>877</v>
       </c>
@@ -15424,7 +15428,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="707" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>877</v>
       </c>
@@ -15438,7 +15442,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>877</v>
       </c>
@@ -15452,7 +15456,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="709" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>877</v>
       </c>
@@ -15466,7 +15470,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="710" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>877</v>
       </c>
@@ -15508,7 +15512,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>877</v>
       </c>
@@ -15522,7 +15526,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A714" t="s">
         <v>877</v>
       </c>
@@ -15536,7 +15540,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A715" t="s">
         <v>877</v>
       </c>
@@ -15578,7 +15582,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="718" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A718" t="s">
         <v>877</v>
       </c>
@@ -15592,7 +15596,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A719" t="s">
         <v>877</v>
       </c>
@@ -15606,7 +15610,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A720" t="s">
         <v>877</v>
       </c>
@@ -15620,7 +15624,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="721" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A721" t="s">
         <v>877</v>
       </c>
@@ -15634,7 +15638,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A722" t="s">
         <v>877</v>
       </c>
@@ -15648,7 +15652,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="723" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A723" t="s">
         <v>877</v>
       </c>
@@ -15662,7 +15666,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A724" t="s">
         <v>877</v>
       </c>
@@ -15690,7 +15694,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="726" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A726" t="s">
         <v>877</v>
       </c>
@@ -15704,7 +15708,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="727" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A727" t="s">
         <v>877</v>
       </c>
@@ -15718,7 +15722,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="728" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A728" t="s">
         <v>877</v>
       </c>
@@ -15732,7 +15736,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="729" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A729" t="s">
         <v>877</v>
       </c>
@@ -15746,7 +15750,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="730" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A730" t="s">
         <v>877</v>
       </c>
@@ -15760,7 +15764,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="731" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A731" t="s">
         <v>877</v>
       </c>
@@ -15774,7 +15778,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="732" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A732" t="s">
         <v>877</v>
       </c>
@@ -15788,7 +15792,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="733" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A733" t="s">
         <v>877</v>
       </c>
@@ -15802,7 +15806,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="734" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A734" t="s">
         <v>877</v>
       </c>
@@ -15830,7 +15834,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="736" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A736" t="s">
         <v>877</v>
       </c>
@@ -15844,7 +15848,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="737" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A737" t="s">
         <v>877</v>
       </c>
@@ -15858,7 +15862,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A738" t="s">
         <v>877</v>
       </c>
@@ -15872,7 +15876,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A739" t="s">
         <v>877</v>
       </c>
@@ -15886,7 +15890,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A740" t="s">
         <v>877</v>
       </c>
@@ -15900,7 +15904,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="741" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A741" t="s">
         <v>877</v>
       </c>
@@ -15914,7 +15918,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="742" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A742" t="s">
         <v>877</v>
       </c>
@@ -15928,7 +15932,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="743" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A743" t="s">
         <v>877</v>
       </c>
@@ -15942,7 +15946,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A744" t="s">
         <v>877</v>
       </c>
@@ -15956,7 +15960,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A745" t="s">
         <v>877</v>
       </c>
@@ -15970,7 +15974,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A746" t="s">
         <v>877</v>
       </c>
@@ -15984,7 +15988,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="747" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A747" t="s">
         <v>877</v>
       </c>
@@ -15998,7 +16002,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="748" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A748" t="s">
         <v>877</v>
       </c>
@@ -16012,7 +16016,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="749" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A749" t="s">
         <v>877</v>
       </c>
@@ -16026,7 +16030,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="750" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A750" t="s">
         <v>877</v>
       </c>
@@ -16068,7 +16072,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A753" t="s">
         <v>877</v>
       </c>
@@ -16082,7 +16086,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="754" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A754" t="s">
         <v>877</v>
       </c>
@@ -16096,7 +16100,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="755" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A755" t="s">
         <v>877</v>
       </c>
@@ -16110,7 +16114,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="756" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A756" t="s">
         <v>877</v>
       </c>
@@ -16124,7 +16128,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="757" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757" t="s">
         <v>877</v>
       </c>
@@ -16138,7 +16142,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A758" t="s">
         <v>877</v>
       </c>
@@ -16152,7 +16156,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A759" t="s">
         <v>877</v>
       </c>
@@ -16166,7 +16170,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A760" t="s">
         <v>877</v>
       </c>
@@ -16180,7 +16184,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A761" t="s">
         <v>877</v>
       </c>
@@ -16194,7 +16198,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="762" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
         <v>877</v>
       </c>
@@ -16208,7 +16212,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="763" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A763" t="s">
         <v>877</v>
       </c>
@@ -16222,7 +16226,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="764" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
         <v>877</v>
       </c>
@@ -16236,7 +16240,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="765" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A765" t="s">
         <v>877</v>
       </c>
@@ -16264,7 +16268,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A767" t="s">
         <v>877</v>
       </c>
@@ -16278,7 +16282,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="768" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
         <v>877</v>
       </c>
@@ -16292,7 +16296,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="769" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
         <v>877</v>
       </c>
@@ -16306,7 +16310,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="770" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
         <v>877</v>
       </c>
@@ -16320,7 +16324,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="771" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
         <v>877</v>
       </c>
@@ -16334,7 +16338,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
         <v>877</v>
       </c>
@@ -16348,7 +16352,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="773" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A773" t="s">
         <v>877</v>
       </c>
@@ -16362,7 +16366,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="774" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
         <v>877</v>
       </c>
@@ -16376,7 +16380,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="775" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A775" t="s">
         <v>877</v>
       </c>
@@ -16390,7 +16394,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="776" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
         <v>877</v>
       </c>
@@ -16404,7 +16408,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="777" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A777" t="s">
         <v>877</v>
       </c>
@@ -16418,7 +16422,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="778" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A778" t="s">
         <v>877</v>
       </c>
@@ -16432,7 +16436,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="779" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A779" t="s">
         <v>877</v>
       </c>
@@ -16446,7 +16450,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="780" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A780" t="s">
         <v>877</v>
       </c>
@@ -16460,7 +16464,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="781" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A781" t="s">
         <v>877</v>
       </c>
@@ -16488,7 +16492,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="783" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A783" t="s">
         <v>877</v>
       </c>
@@ -16502,7 +16506,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="784" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
         <v>877</v>
       </c>
@@ -16516,7 +16520,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="785" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A785" t="s">
         <v>877</v>
       </c>
@@ -16530,7 +16534,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="786" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
         <v>877</v>
       </c>
@@ -16544,7 +16548,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="787" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A787" t="s">
         <v>877</v>
       </c>
@@ -16558,7 +16562,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="788" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A788" t="s">
         <v>877</v>
       </c>
@@ -16572,7 +16576,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="789" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
         <v>877</v>
       </c>
@@ -16586,7 +16590,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="790" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A790" t="s">
         <v>877</v>
       </c>
@@ -16611,7 +16615,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="792" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A792" t="s">
         <v>877</v>
       </c>
@@ -16625,7 +16629,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="793" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
         <v>877</v>
       </c>
@@ -16639,7 +16643,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="794" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A794" t="s">
         <v>877</v>
       </c>
@@ -16653,7 +16657,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="795" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A795" t="s">
         <v>877</v>
       </c>
@@ -16664,7 +16668,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="796" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A796" t="s">
         <v>877</v>
       </c>
@@ -16675,7 +16679,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="797" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A797" t="s">
         <v>877</v>
       </c>
@@ -16689,7 +16693,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="798" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
         <v>877</v>
       </c>
@@ -16703,7 +16707,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="799" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
         <v>877</v>
       </c>
@@ -16717,7 +16721,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="800" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A800" t="s">
         <v>877</v>
       </c>
@@ -16731,7 +16735,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="801" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A801" t="s">
         <v>877</v>
       </c>
@@ -16745,7 +16749,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="802" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A802" t="s">
         <v>877</v>
       </c>
@@ -16759,7 +16763,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="803" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A803" t="s">
         <v>877</v>
       </c>
@@ -16773,7 +16777,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="804" spans="1:4" ht="114" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:4" ht="114" hidden="1" x14ac:dyDescent="0.45">
       <c r="A804" t="s">
         <v>877</v>
       </c>
@@ -16787,7 +16791,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="805" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A805" t="s">
         <v>877</v>
       </c>
@@ -16801,7 +16805,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="806" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A806" t="s">
         <v>877</v>
       </c>
@@ -16815,7 +16819,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="807" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A807" t="s">
         <v>877</v>
       </c>
@@ -16829,7 +16833,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="808" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A808" t="s">
         <v>877</v>
       </c>
@@ -16843,7 +16847,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="809" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A809" t="s">
         <v>877</v>
       </c>
@@ -16857,7 +16861,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="810" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A810" t="s">
         <v>877</v>
       </c>
@@ -16871,7 +16875,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="811" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A811" t="s">
         <v>877</v>
       </c>
@@ -16885,7 +16889,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="812" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A812" t="s">
         <v>877</v>
       </c>
@@ -16899,7 +16903,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="813" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A813" t="s">
         <v>877</v>
       </c>
@@ -16913,7 +16917,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="814" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A814" t="s">
         <v>877</v>
       </c>
@@ -16927,7 +16931,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="815" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A815" t="s">
         <v>877</v>
       </c>
@@ -16941,7 +16945,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="816" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A816" t="s">
         <v>877</v>
       </c>
@@ -16955,7 +16959,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="817" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A817" t="s">
         <v>877</v>
       </c>
@@ -16969,7 +16973,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="818" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
         <v>1365</v>
       </c>
@@ -17011,7 +17015,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="821" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821" t="s">
         <v>1365</v>
       </c>
@@ -17025,7 +17029,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="822" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A822" t="s">
         <v>1365</v>
       </c>
@@ -17039,7 +17043,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="823" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A823" t="s">
         <v>1365</v>
       </c>
@@ -17053,7 +17057,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="824" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824" t="s">
         <v>1365</v>
       </c>
@@ -17067,7 +17071,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="825" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825" t="s">
         <v>1365</v>
       </c>
@@ -17081,7 +17085,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="826" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826" t="s">
         <v>1365</v>
       </c>
@@ -17095,7 +17099,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="827" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A827" t="s">
         <v>1365</v>
       </c>
@@ -17109,7 +17113,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="828" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A828" t="s">
         <v>1365</v>
       </c>
@@ -17123,7 +17127,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829" t="s">
         <v>1365</v>
       </c>
@@ -17151,7 +17155,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="831" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A831" t="s">
         <v>1365</v>
       </c>
@@ -17165,7 +17169,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="832" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A832" t="s">
         <v>1365</v>
       </c>
@@ -17179,7 +17183,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="833" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833" t="s">
         <v>1365</v>
       </c>
@@ -17193,7 +17197,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="834" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A834" t="s">
         <v>1365</v>
       </c>
@@ -17207,7 +17211,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="835" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835" t="s">
         <v>1365</v>
       </c>
@@ -17221,7 +17225,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="836" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836" t="s">
         <v>1365</v>
       </c>
@@ -17235,7 +17239,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="837" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837" t="s">
         <v>1365</v>
       </c>
@@ -17305,7 +17309,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="842" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A842" t="s">
         <v>1365</v>
       </c>
@@ -17319,7 +17323,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="843" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A843" t="s">
         <v>1365</v>
       </c>
@@ -17333,7 +17337,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="844" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A844" t="s">
         <v>1365</v>
       </c>
@@ -17347,7 +17351,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="845" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845" t="s">
         <v>1365</v>
       </c>
@@ -17361,7 +17365,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="846" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A846" t="s">
         <v>1365</v>
       </c>
@@ -17375,7 +17379,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="847" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A847" t="s">
         <v>1365</v>
       </c>
@@ -17389,7 +17393,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="848" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A848" t="s">
         <v>1365</v>
       </c>
@@ -17403,7 +17407,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="849" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849" t="s">
         <v>1365</v>
       </c>
@@ -17417,7 +17421,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="850" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A850" t="s">
         <v>1365</v>
       </c>
@@ -17431,7 +17435,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="851" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A851" t="s">
         <v>1365</v>
       </c>
@@ -17445,7 +17449,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="852" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="852" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A852" t="s">
         <v>1365</v>
       </c>
@@ -17459,7 +17463,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="853" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A853" t="s">
         <v>1365</v>
       </c>
@@ -17473,7 +17477,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="854" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854" t="s">
         <v>1365</v>
       </c>
@@ -17487,7 +17491,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="855" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A855" t="s">
         <v>1365</v>
       </c>
@@ -17501,7 +17505,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="856" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A856" t="s">
         <v>1365</v>
       </c>
@@ -17515,7 +17519,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="857" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A857" t="s">
         <v>1365</v>
       </c>
@@ -17529,7 +17533,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="858" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858" t="s">
         <v>1365</v>
       </c>
@@ -17543,7 +17547,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="859" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A859" t="s">
         <v>1365</v>
       </c>
@@ -17557,7 +17561,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="860" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A860" t="s">
         <v>1365</v>
       </c>
@@ -17571,7 +17575,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="861" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>1365</v>
       </c>
@@ -17585,7 +17589,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="862" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>1365</v>
       </c>
@@ -17613,7 +17617,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="864" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A864" t="s">
         <v>1365</v>
       </c>
@@ -17627,7 +17631,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="865" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A865" t="s">
         <v>1365</v>
       </c>
@@ -17641,7 +17645,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="866" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>1365</v>
       </c>
@@ -17655,7 +17659,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="867" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A867" t="s">
         <v>1365</v>
       </c>
@@ -17669,7 +17673,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="868" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>1365</v>
       </c>
@@ -17683,7 +17687,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="869" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>1365</v>
       </c>
@@ -17697,7 +17701,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="870" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>1365</v>
       </c>
@@ -17711,7 +17715,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="871" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A871" t="s">
         <v>1365</v>
       </c>
@@ -17725,7 +17729,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="872" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A872" t="s">
         <v>1365</v>
       </c>
@@ -17753,7 +17757,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="874" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>1365</v>
       </c>
@@ -17767,7 +17771,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="875" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>1365</v>
       </c>
@@ -17781,7 +17785,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="876" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A876" t="s">
         <v>1365</v>
       </c>
@@ -17795,7 +17799,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="877" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A877" t="s">
         <v>1365</v>
       </c>
@@ -17809,7 +17813,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="878" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A878" t="s">
         <v>1365</v>
       </c>
@@ -17823,7 +17827,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="879" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A879" t="s">
         <v>1365</v>
       </c>
@@ -17837,7 +17841,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="880" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A880" t="s">
         <v>1365</v>
       </c>
@@ -17865,7 +17869,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="882" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A882" t="s">
         <v>1365</v>
       </c>
@@ -17879,7 +17883,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="883" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="883" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A883" t="s">
         <v>1365</v>
       </c>
@@ -17893,7 +17897,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="884" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A884" t="s">
         <v>1365</v>
       </c>
@@ -17907,7 +17911,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="885" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A885" t="s">
         <v>1365</v>
       </c>
@@ -17921,7 +17925,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="886" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A886" t="s">
         <v>1365</v>
       </c>
@@ -17935,7 +17939,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="887" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A887" t="s">
         <v>1365</v>
       </c>
@@ -17949,7 +17953,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="888" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A888" t="s">
         <v>1365</v>
       </c>
@@ -17963,7 +17967,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="889" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A889" t="s">
         <v>1365</v>
       </c>
@@ -17977,7 +17981,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="890" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A890" t="s">
         <v>1365</v>
       </c>
@@ -17991,7 +17995,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="891" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A891" t="s">
         <v>1365</v>
       </c>
@@ -18005,7 +18009,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="892" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A892" t="s">
         <v>1365</v>
       </c>
@@ -18019,7 +18023,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="893" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A893" t="s">
         <v>1365</v>
       </c>
@@ -18047,7 +18051,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="895" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A895" t="s">
         <v>1365</v>
       </c>
@@ -18061,7 +18065,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="896" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A896" t="s">
         <v>1365</v>
       </c>
@@ -18075,7 +18079,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="897" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A897" t="s">
         <v>1365</v>
       </c>
@@ -18089,7 +18093,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="898" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A898" t="s">
         <v>1365</v>
       </c>
@@ -18103,7 +18107,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="899" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A899" t="s">
         <v>1365</v>
       </c>
@@ -18117,7 +18121,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="900" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A900" t="s">
         <v>1365</v>
       </c>
@@ -18145,7 +18149,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="902" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A902" t="s">
         <v>1365</v>
       </c>
@@ -18159,7 +18163,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="903" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="903" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A903" t="s">
         <v>1365</v>
       </c>
@@ -18173,7 +18177,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="904" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="904" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A904" t="s">
         <v>1365</v>
       </c>
@@ -18201,7 +18205,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="906" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A906" t="s">
         <v>1365</v>
       </c>
@@ -18215,7 +18219,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="907" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A907" t="s">
         <v>1365</v>
       </c>
@@ -18243,7 +18247,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="909" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="909" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A909" t="s">
         <v>1365</v>
       </c>
@@ -18257,7 +18261,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="910" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A910" t="s">
         <v>1365</v>
       </c>
@@ -18285,7 +18289,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="912" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A912" t="s">
         <v>1365</v>
       </c>
@@ -18299,7 +18303,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="913" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A913" t="s">
         <v>1365</v>
       </c>
@@ -18313,7 +18317,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="914" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A914" t="s">
         <v>1365</v>
       </c>
@@ -18327,7 +18331,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="915" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A915" t="s">
         <v>1365</v>
       </c>
@@ -18341,7 +18345,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="916" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A916" t="s">
         <v>1365</v>
       </c>
@@ -18355,7 +18359,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="917" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A917" t="s">
         <v>1365</v>
       </c>
@@ -18369,7 +18373,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="918" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A918" t="s">
         <v>1365</v>
       </c>
@@ -18383,7 +18387,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="919" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="919" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A919" t="s">
         <v>1365</v>
       </c>
@@ -18397,7 +18401,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="920" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A920" t="s">
         <v>1365</v>
       </c>
@@ -18411,7 +18415,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="921" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A921" t="s">
         <v>1365</v>
       </c>
@@ -18425,7 +18429,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="922" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="922" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A922" t="s">
         <v>1365</v>
       </c>
@@ -18439,7 +18443,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="923" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="923" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A923" t="s">
         <v>1365</v>
       </c>
@@ -18453,7 +18457,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="924" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="924" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A924" t="s">
         <v>1365</v>
       </c>
@@ -18467,7 +18471,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="925" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="925" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A925" t="s">
         <v>1365</v>
       </c>
@@ -18481,7 +18485,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="926" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="926" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A926" t="s">
         <v>1365</v>
       </c>
@@ -18495,7 +18499,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="927" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="927" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A927" t="s">
         <v>1365</v>
       </c>
@@ -18509,7 +18513,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="928" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="928" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A928" t="s">
         <v>1365</v>
       </c>
@@ -18523,7 +18527,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="929" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="929" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A929" t="s">
         <v>1365</v>
       </c>
@@ -18537,7 +18541,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="930" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="930" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A930" t="s">
         <v>1365</v>
       </c>
@@ -18551,7 +18555,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="931" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="931" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A931" t="s">
         <v>1365</v>
       </c>
@@ -18565,7 +18569,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="932" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="932" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A932" t="s">
         <v>1365</v>
       </c>
@@ -18579,7 +18583,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="933" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="933" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A933" t="s">
         <v>1365</v>
       </c>
@@ -18593,7 +18597,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="934" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="934" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A934" t="s">
         <v>1365</v>
       </c>
@@ -18607,7 +18611,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="935" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="935" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A935" t="s">
         <v>1365</v>
       </c>
@@ -18621,7 +18625,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="936" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="936" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A936" t="s">
         <v>1365</v>
       </c>
@@ -18635,7 +18639,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="937" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="937" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A937" t="s">
         <v>1365</v>
       </c>
@@ -18649,7 +18653,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="938" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="938" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A938" t="s">
         <v>1365</v>
       </c>
@@ -18663,7 +18667,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="939" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="939" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A939" t="s">
         <v>1365</v>
       </c>
@@ -18677,7 +18681,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="940" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="940" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A940" t="s">
         <v>1365</v>
       </c>
@@ -18691,7 +18695,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="941" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="941" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A941" t="s">
         <v>1365</v>
       </c>
@@ -18705,7 +18709,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="942" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="942" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A942" t="s">
         <v>1365</v>
       </c>
@@ -18719,7 +18723,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="943" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="943" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A943" t="s">
         <v>1365</v>
       </c>
@@ -18733,7 +18737,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="944" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="944" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A944" t="s">
         <v>1365</v>
       </c>
@@ -18747,7 +18751,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="945" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="945" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A945" t="s">
         <v>1365</v>
       </c>
@@ -18761,7 +18765,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="946" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="946" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A946" t="s">
         <v>1365</v>
       </c>
@@ -18775,7 +18779,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="947" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="947" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A947" t="s">
         <v>1365</v>
       </c>
@@ -18789,7 +18793,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="948" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="948" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A948" t="s">
         <v>1365</v>
       </c>
@@ -18845,7 +18849,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="952" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="952" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A952" t="s">
         <v>1365</v>
       </c>
@@ -18859,7 +18863,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="953" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="953" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A953" t="s">
         <v>1365</v>
       </c>
@@ -18873,7 +18877,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="954" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="954" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A954" t="s">
         <v>1365</v>
       </c>
@@ -18887,7 +18891,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="955" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="955" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A955" t="s">
         <v>1365</v>
       </c>
@@ -18895,7 +18899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="956" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="956" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A956" t="s">
         <v>1365</v>
       </c>
@@ -18909,7 +18913,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="957" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="957" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A957" t="s">
         <v>1365</v>
       </c>
@@ -18923,7 +18927,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="958" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="958" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A958" t="s">
         <v>1365</v>
       </c>
@@ -18937,7 +18941,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="959" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="959" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A959" t="s">
         <v>1365</v>
       </c>
@@ -18951,7 +18955,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="960" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="960" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A960" t="s">
         <v>1365</v>
       </c>
@@ -18965,7 +18969,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="961" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="961" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A961" t="s">
         <v>1365</v>
       </c>
@@ -18979,7 +18983,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="962" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="962" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A962" t="s">
         <v>1365</v>
       </c>
@@ -18993,7 +18997,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="963" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="963" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A963" t="s">
         <v>1365</v>
       </c>
@@ -19007,7 +19011,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="964" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="964" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A964" t="s">
         <v>1365</v>
       </c>
@@ -19021,7 +19025,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="965" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A965" t="s">
         <v>1365</v>
       </c>
@@ -19035,7 +19039,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="966" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="966" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A966" t="s">
         <v>1365</v>
       </c>
@@ -19049,7 +19053,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="967" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="967" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A967" t="s">
         <v>1365</v>
       </c>
@@ -19063,7 +19067,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="968" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="968" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A968" t="s">
         <v>1365</v>
       </c>
@@ -19077,7 +19081,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="969" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="969" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A969" t="s">
         <v>1364</v>
       </c>
@@ -19091,7 +19095,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="970" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="970" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A970" t="s">
         <v>1364</v>
       </c>
@@ -19119,7 +19123,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="972" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="972" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A972" t="s">
         <v>1364</v>
       </c>
@@ -19133,7 +19137,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="973" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="973" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A973" t="s">
         <v>1364</v>
       </c>
@@ -19147,7 +19151,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="974" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="974" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A974" t="s">
         <v>1364</v>
       </c>
@@ -19161,7 +19165,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="975" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="975" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A975" t="s">
         <v>1364</v>
       </c>
@@ -19175,7 +19179,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="976" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="976" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A976" t="s">
         <v>1364</v>
       </c>
@@ -19189,7 +19193,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="977" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="977" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A977" t="s">
         <v>1364</v>
       </c>
@@ -19203,7 +19207,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="978" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="978" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A978" t="s">
         <v>1364</v>
       </c>
@@ -19217,7 +19221,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="979" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="979" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A979" t="s">
         <v>1364</v>
       </c>
@@ -19231,7 +19235,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="980" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="980" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A980" t="s">
         <v>1364</v>
       </c>
@@ -19245,7 +19249,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="981" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="981" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A981" t="s">
         <v>1364</v>
       </c>
@@ -19273,7 +19277,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="983" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="983" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A983" t="s">
         <v>1364</v>
       </c>
@@ -19287,7 +19291,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="984" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="984" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A984" t="s">
         <v>1364</v>
       </c>
@@ -19301,7 +19305,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="985" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="985" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A985" t="s">
         <v>1364</v>
       </c>
@@ -19315,7 +19319,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="986" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="986" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A986" t="s">
         <v>1364</v>
       </c>
@@ -19329,7 +19333,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="987" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="987" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A987" t="s">
         <v>1364</v>
       </c>
@@ -19343,7 +19347,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="988" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="988" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A988" t="s">
         <v>1364</v>
       </c>
@@ -19357,7 +19361,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="989" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="989" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A989" t="s">
         <v>1364</v>
       </c>
@@ -19371,7 +19375,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="990" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="990" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A990" t="s">
         <v>1364</v>
       </c>
@@ -19385,7 +19389,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="991" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="991" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A991" t="s">
         <v>1364</v>
       </c>
@@ -19399,7 +19403,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="992" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="992" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A992" t="s">
         <v>1364</v>
       </c>
@@ -19413,7 +19417,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="993" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="993" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A993" t="s">
         <v>1364</v>
       </c>
@@ -19427,7 +19431,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="994" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="994" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A994" t="s">
         <v>1364</v>
       </c>
@@ -19441,7 +19445,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="995" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="995" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A995" t="s">
         <v>1364</v>
       </c>
@@ -19455,7 +19459,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="996" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="996" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A996" t="s">
         <v>1364</v>
       </c>
@@ -19469,7 +19473,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="997" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="997" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A997" t="s">
         <v>1364</v>
       </c>
@@ -19483,7 +19487,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="998" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A998" t="s">
         <v>1364</v>
       </c>
@@ -19497,7 +19501,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="999" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="999" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A999" t="s">
         <v>1364</v>
       </c>
@@ -19525,7 +19529,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="1001" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1001" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1001" t="s">
         <v>1364</v>
       </c>
@@ -19539,7 +19543,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="1002" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1002" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1002" t="s">
         <v>1364</v>
       </c>
@@ -19553,7 +19557,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="1003" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1003" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1003" t="s">
         <v>1364</v>
       </c>
@@ -19567,7 +19571,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="1004" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1004" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1004" t="s">
         <v>1364</v>
       </c>
@@ -19581,7 +19585,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="1005" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1005" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1005" t="s">
         <v>1364</v>
       </c>
@@ -19609,7 +19613,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="1007" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1007" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1007" t="s">
         <v>1364</v>
       </c>
@@ -19623,7 +19627,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="1008" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1008" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1008" t="s">
         <v>1364</v>
       </c>
@@ -19637,7 +19641,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="1009" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1009" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1009" t="s">
         <v>1364</v>
       </c>
@@ -19665,7 +19669,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="1011" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1011" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1011" t="s">
         <v>1364</v>
       </c>
@@ -19679,7 +19683,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="1012" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1012" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1012" t="s">
         <v>1364</v>
       </c>
@@ -19693,7 +19697,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="1013" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1013" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1013" t="s">
         <v>1364</v>
       </c>
@@ -19707,7 +19711,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="1014" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1014" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1014" t="s">
         <v>1364</v>
       </c>
@@ -19721,7 +19725,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="1015" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1015" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1015" t="s">
         <v>1364</v>
       </c>
@@ -19735,7 +19739,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="1016" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1016" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1016" t="s">
         <v>1364</v>
       </c>
@@ -19749,7 +19753,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="1017" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1017" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1017" t="s">
         <v>1364</v>
       </c>
@@ -19763,7 +19767,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="1018" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1018" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A1018" t="s">
         <v>1364</v>
       </c>
@@ -19778,7 +19782,91 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1018" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}"/>
+  <autoFilter ref="A1:I1018" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0, 10"/>
+        <filter val="0,10, 17"/>
+        <filter val="1, 10"/>
+        <filter val="1, 10, 11"/>
+        <filter val="1, 10, 11, 13"/>
+        <filter val="1, 10, 17"/>
+        <filter val="1, 10, 17, 16"/>
+        <filter val="1, 10, 7, 2"/>
+        <filter val="1, 10, 8"/>
+        <filter val="1, 17, 10"/>
+        <filter val="1, 2, 10"/>
+        <filter val="1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 16, 17"/>
+        <filter val="1, 3, 10"/>
+        <filter val="1, 3, 4, 10"/>
+        <filter val="1, 4, 10, 11"/>
+        <filter val="1, 5, 8, 10"/>
+        <filter val="1, 7, 11, 10"/>
+        <filter val="1, 8, 10"/>
+        <filter val="1, 8, 10, 13, 17"/>
+        <filter val="10"/>
+        <filter val="10, 0"/>
+        <filter val="10, 1"/>
+        <filter val="10, 1, 9"/>
+        <filter val="10, 11"/>
+        <filter val="10, 16"/>
+        <filter val="10, 16, 17"/>
+        <filter val="10, 17"/>
+        <filter val="10, 17, 0"/>
+        <filter val="10, 17, 13"/>
+        <filter val="10, 2"/>
+        <filter val="10, 3"/>
+        <filter val="10, 5"/>
+        <filter val="10, 8, 17"/>
+        <filter val="11, 10"/>
+        <filter val="11, 10, 16"/>
+        <filter val="12, 10"/>
+        <filter val="13, 10, 17"/>
+        <filter val="13, 11, 10"/>
+        <filter val="13, 12, 8, 10, 16, 17"/>
+        <filter val="13, 7, 10"/>
+        <filter val="15, 10, 12"/>
+        <filter val="16, 10"/>
+        <filter val="16, 10, 4"/>
+        <filter val="16, 4, 10"/>
+        <filter val="16, 5, 10"/>
+        <filter val="17, 10"/>
+        <filter val="17, 10, 1"/>
+        <filter val="17, 10, 13, 8"/>
+        <filter val="17, 10, 8"/>
+        <filter val="17, 13, 10"/>
+        <filter val="17, 16, 10"/>
+        <filter val="17, 7, 13, 10"/>
+        <filter val="17, 9, 10"/>
+        <filter val="2, 1, 10"/>
+        <filter val="2, 10"/>
+        <filter val="2, 12, 10"/>
+        <filter val="2, 5, 10"/>
+        <filter val="3, 1, 10"/>
+        <filter val="3, 10"/>
+        <filter val="3, 10, 16"/>
+        <filter val="3, 4, 6, 11, 10, 1, 13"/>
+        <filter val="3, 5, 10"/>
+        <filter val="3, 5. 10"/>
+        <filter val="4, 10"/>
+        <filter val="4, 10, 1"/>
+        <filter val="4, 10, 16"/>
+        <filter val="4, 5, 10"/>
+        <filter val="4, 8, 5,9, 10"/>
+        <filter val="4, 9, 10"/>
+        <filter val="5, 10"/>
+        <filter val="5, 10, 4"/>
+        <filter val="7, 10"/>
+        <filter val="7, 8, 10, 13"/>
+        <filter val="7, 8, 9, 10, 11"/>
+        <filter val="8, 10"/>
+        <filter val="8, 10, 13"/>
+        <filter val="9, 10"/>
+        <filter val="9, 10, 17"/>
+        <filter val="9, 5, 13, 10"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
+++ b/Data/Annotations/TFM-ExtractedArgumentsAnnotations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upvedues-my.sharepoint.com/personal/cpaltat_upv_edu_es/Documents/TFM/Data/Annotations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3197" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E94D9DA-2909-44A8-BA9A-561C743192C5}"/>
+  <xr:revisionPtr revIDLastSave="3201" documentId="8_{6D7F9241-FBBC-4916-8F78-D1B055A11915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08B57E79-5F16-47C9-9DF2-597BBB7D0AF4}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{49184B03-C425-4292-8179-3E0C1E060977}"/>
   </bookViews>
@@ -5550,7 +5550,7 @@
   <cols>
     <col min="1" max="1" width="43.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="112.86328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="163.06640625" style="6" customWidth="1"/>
     <col min="5" max="5" width="1.796875" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.9296875" customWidth="1"/>
     <col min="7" max="7" width="2.86328125" style="15" bestFit="1" customWidth="1"/>
@@ -5657,7 +5657,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>447</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>447</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>447</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>447</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>447</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>447</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>447</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>447</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>447</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>447</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>447</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>447</v>
       </c>
@@ -6600,7 +6600,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>447</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>447</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>447</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>447</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>447</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>447</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>447</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>447</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>447</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>447</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="153" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>447</v>
       </c>
@@ -7734,7 +7734,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>447</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>447</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>447</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>447</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="203" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:4" ht="99.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A203" t="s">
         <v>447</v>
       </c>
@@ -8557,7 +8557,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A216" t="s">
         <v>447</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>447</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:4" ht="85.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A232" t="s">
         <v>447</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="248" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A248" t="s">
         <v>449</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="250" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A250" t="s">
         <v>449</v>
       </c>
@@ -9044,7 +9044,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A251" t="s">
         <v>449</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="252" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A252" t="s">
         <v>449</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A253" t="s">
         <v>449</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="254" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A254" t="s">
         <v>449</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="255" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:4" ht="71.25" hidden="1" x14ac:dyDescent="0.45">
       <c r="A255" t="s">
         <v>449</v>
       </c>
@@ -9114,7 +9114,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="256" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
         <v>449</v>
       </c>
@@ -9128,7 +9128,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="257" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A257" t="s">
         <v>449</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="258" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A258" t="s">
         <v>449</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="259" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A259" t="s">
         <v>449</v>
       </c>
@@ -9170,7 +9170,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A260" t="s">
         <v>449</v>
       </c>
@@ -9184,7 +9184,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="261" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A261" t="s">
         <v>449</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="262" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A262" t="s">
         <v>449</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
         <v>449</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="264" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A264" t="s">
         <v>449</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="265" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>449</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>449</v>
       </c>
@@ -9268,7 +9268,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="267" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A267" t="s">
         <v>449</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="268" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A268" t="s">
         <v>449</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="269" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="270" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
         <v>449</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="271" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A271" t="s">
         <v>449</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="292" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A292" t="s">
         <v>449</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="293" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A293" t="s">
         <v>449</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="298" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A298" t="s">
         <v>449</v>
       </c>
@@ -9758,7 +9758,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="302" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A302" t="s">
         <v>449</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="305" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" t="s">
         <v>449</v>
       </c>
@@ -9828,7 +9828,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="307" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
         <v>449</v>
       </c>
@@ -9842,7 +9842,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="308" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A308" t="s">
         <v>449</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="309" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A309" t="s">
         <v>449</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A311" t="s">
         <v>449</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="316" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A316" t="s">
         <v>449</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="319" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A319" t="s">
         <v>449</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A320" t="s">
         <v>449</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="325" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A325" t="s">
         <v>449</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="331" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
         <v>449</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A336" t="s">
         <v>449</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
         <v>449</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="341" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A341" t="s">
         <v>449</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A342" t="s">
         <v>449</v>
       </c>
@@ -10332,7 +10332,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="343" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A343" t="s">
         <v>449</v>
       </c>
@@ -10346,7 +10346,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A344" t="s">
         <v>449</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A348" t="s">
         <v>449</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="350" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A350" t="s">
         <v>449</v>
       </c>
@@ -10444,7 +10444,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="351" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A351" t="s">
         <v>449</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="353" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A353" t="s">
         <v>449</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="354" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A354" t="s">
         <v>449</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="357" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A357" t="s">
         <v>449</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="358" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A358" t="s">
         <v>449</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A360" t="s">
         <v>449</v>
       </c>
@@ -10640,7 +10640,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="365" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A365" t="s">
         <v>449</v>
       </c>
@@ -10654,7 +10654,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A366" t="s">
         <v>449</v>
       </c>
@@ -10668,7 +10668,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="367" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A367" t="s">
         <v>449</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="368" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A368" t="s">
         <v>449</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>449</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A374" t="s">
         <v>449</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="376" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A376" t="s">
         <v>449</v>
       </c>
@@ -10808,7 +10808,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="377" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A377" t="s">
         <v>449</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="378" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A378" t="s">
         <v>449</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="379" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
         <v>449</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="383" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A383" t="s">
         <v>449</v>
       </c>
@@ -10906,7 +10906,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="384" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A384" t="s">
         <v>449</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="391" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A391" t="s">
         <v>449</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A392" t="s">
         <v>449</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="393" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A393" t="s">
         <v>449</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="394" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A394" t="s">
         <v>449</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="397" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A397" t="s">
         <v>449</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="399" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A399" t="s">
         <v>449</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="403" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
         <v>449</v>
       </c>
@@ -11214,7 +11214,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A406" t="s">
         <v>449</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A407" t="s">
         <v>449</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="409" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A409" t="s">
         <v>449</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A411" t="s">
         <v>449</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="412" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A412" t="s">
         <v>449</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A413" t="s">
         <v>449</v>
       </c>
@@ -11326,7 +11326,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="414" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A414" t="s">
         <v>449</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="417" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A417" t="s">
         <v>449</v>
       </c>
@@ -11396,7 +11396,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A419" t="s">
         <v>449</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A420" t="s">
         <v>449</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="421" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A421" t="s">
         <v>449</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A422" t="s">
         <v>449</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A423" t="s">
         <v>449</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A424" t="s">
         <v>449</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A425" t="s">
         <v>449</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A426" t="s">
         <v>449</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A432" t="s">
         <v>449</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A434" t="s">
         <v>449</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A435" t="s">
         <v>449</v>
       </c>
@@ -11634,7 +11634,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A436" t="s">
         <v>449</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A438" t="s">
         <v>449</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A439" t="s">
         <v>449</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A440" t="s">
         <v>449</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A441" t="s">
         <v>449</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A442" t="s">
         <v>449</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A443" t="s">
         <v>449</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A444" t="s">
         <v>449</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A446" t="s">
         <v>449</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A447" t="s">
         <v>449</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A448" t="s">
         <v>449</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="449" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>449</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="450" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>449</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="451" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>449</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="454" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>449</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>449</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="456" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>449</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>449</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="463" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>449</v>
       </c>
@@ -12026,7 +12026,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="464" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
         <v>449</v>
       </c>
@@ -12068,7 +12068,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="467" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
         <v>449</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="468" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
         <v>449</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
         <v>449</v>
       </c>
@@ -12110,7 +12110,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="470" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
         <v>449</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="472" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
         <v>449</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="478" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
         <v>449</v>
       </c>
@@ -12236,7 +12236,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="479" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
         <v>449</v>
       </c>
@@ -12278,7 +12278,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="482" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
         <v>449</v>
       </c>
@@ -12348,7 +12348,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="487" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
         <v>449</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="489" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
         <v>449</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="490" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
         <v>449</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="491" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
         <v>449</v>
       </c>
@@ -12488,7 +12488,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
         <v>449</v>
       </c>
@@ -12530,7 +12530,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="500" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
         <v>449</v>
       </c>
@@ -12600,7 +12600,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
         <v>449</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A506" t="s">
         <v>449</v>
       </c>
@@ -12628,7 +12628,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="507" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A507" t="s">
         <v>449</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="508" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A508" t="s">
         <v>449</v>
       </c>
@@ -12656,7 +12656,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="509" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A509" t="s">
         <v>449</v>
       </c>
@@ -12670,7 +12670,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A510" t="s">
         <v>449</v>
       </c>
@@ -12698,7 +12698,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="512" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A512" t="s">
         <v>449</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="513" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A513" t="s">
         <v>449</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A514" t="s">
         <v>449</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="515" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A515" t="s">
         <v>449</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="516" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A516" t="s">
         <v>449</v>
       </c>
@@ -12768,7 +12768,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="517" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A517" t="s">
         <v>449</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="518" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A518" t="s">
         <v>449</v>
       </c>
@@ -12796,7 +12796,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A519" t="s">
         <v>449</v>
       </c>
@@ -12810,7 +12810,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A520" t="s">
         <v>449</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="521" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A521" t="s">
         <v>449</v>
       </c>
@@ -12838,7 +12838,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="522" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A522" t="s">
         <v>449</v>
       </c>
@@ -12908,7 +12908,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A527" t="s">
         <v>449</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="529" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A529" t="s">
         <v>449</v>
       </c>
@@ -12950,7 +12950,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="530" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A530" t="s">
         <v>449</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A533" t="s">
         <v>449</v>
       </c>
@@ -13006,7 +13006,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="534" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A534" t="s">
         <v>449</v>
       </c>
@@ -13020,7 +13020,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A535" t="s">
         <v>449</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="536" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A536" t="s">
         <v>449</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A537" t="s">
         <v>449</v>
       </c>
@@ -13132,7 +13132,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="543" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A543" t="s">
         <v>449</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A551" t="s">
         <v>449</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="553" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A553" t="s">
         <v>449</v>
       </c>
@@ -13286,7 +13286,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="554" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A554" t="s">
         <v>449</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A557" t="s">
         <v>449</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A559" t="s">
         <v>449</v>
       </c>
@@ -13440,7 +13440,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="565" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A565" t="s">
         <v>449</v>
       </c>
@@ -13496,7 +13496,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="569" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A569" t="s">
         <v>449</v>
       </c>
@@ -13566,7 +13566,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="574" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A574" t="s">
         <v>449</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="575" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A575" t="s">
         <v>449</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="576" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A576" t="s">
         <v>449</v>
       </c>
@@ -13608,7 +13608,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="577" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A577" t="s">
         <v>449</v>
       </c>
@@ -13636,7 +13636,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="579" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A579" t="s">
         <v>449</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="586" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A586" t="s">
         <v>449</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="587" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A587" t="s">
         <v>449</v>
       </c>
@@ -13762,7 +13762,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="588" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A588" t="s">
         <v>449</v>
       </c>
@@ -13776,7 +13776,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="589" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A589" t="s">
         <v>449</v>
       </c>
@@ -13790,7 +13790,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="590" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A590" t="s">
         <v>449</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="598" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A598" t="s">
         <v>449</v>
       </c>
@@ -13916,7 +13916,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="599" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A599" t="s">
         <v>449</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="600" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A600" t="s">
         <v>449</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A602" t="s">
         <v>449</v>
       </c>
@@ -13972,7 +13972,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="603" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A603" t="s">
         <v>449</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="604" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A604" t="s">
         <v>449</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="607" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A607" t="s">
         <v>449</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="608" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A608" t="s">
         <v>449</v>
       </c>
@@ -14056,7 +14056,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="609" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A609" t="s">
         <v>449</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="610" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A610" t="s">
         <v>449</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="611" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A611" t="s">
         <v>449</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="616" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A616" t="s">
         <v>449</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="618" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A618" t="s">
         <v>449</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A621" t="s">
         <v>449</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="632" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A632" t="s">
         <v>449</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="633" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A633" t="s">
         <v>449</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="638" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A638" t="s">
         <v>449</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="640" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A640" t="s">
         <v>449</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="642" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A642" t="s">
         <v>449</v>
       </c>
@@ -14616,7 +14616,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="649" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A649" t="s">
         <v>449</v>
       </c>
@@ -14644,7 +14644,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="651" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A651" t="s">
         <v>449</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="654" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A654" t="s">
         <v>877</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="655" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A655" t="s">
         <v>877</v>
       </c>
@@ -14798,7 +14798,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="662" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A662" t="s">
         <v>877</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="664" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A664" t="s">
         <v>877</v>
       </c>
@@ -14854,7 +14854,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A666" t="s">
         <v>877</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="668" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A668" t="s">
         <v>877</v>
       </c>
@@ -14896,7 +14896,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="669" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A669" t="s">
         <v>877</v>
       </c>
@@ -14910,7 +14910,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="670" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A670" t="s">
         <v>877</v>
       </c>
@@ -14938,7 +14938,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="672" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A672" t="s">
         <v>877</v>
       </c>
@@ -14966,7 +14966,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="674" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A674" t="s">
         <v>877</v>
       </c>
@@ -15008,7 +15008,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="677" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A677" t="s">
         <v>877</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="678" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A678" t="s">
         <v>877</v>
       </c>
@@ -15036,7 +15036,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="679" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A679" t="s">
         <v>877</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="686" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A686" t="s">
         <v>877</v>
       </c>
@@ -15148,7 +15148,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="687" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A687" t="s">
         <v>877</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="688" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A688" t="s">
         <v>877</v>
       </c>
@@ -15176,7 +15176,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="689" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A689" t="s">
         <v>877</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="691" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A691" t="s">
         <v>877</v>
       </c>
@@ -15232,7 +15232,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="693" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A693" t="s">
         <v>877</v>
       </c>
@@ -15260,7 +15260,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="695" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A695" t="s">
         <v>877</v>
       </c>
@@ -15386,7 +15386,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="704" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A704" t="s">
         <v>877</v>
       </c>
@@ -15414,7 +15414,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="706" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A706" t="s">
         <v>877</v>
       </c>
@@ -15428,7 +15428,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="707" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A707" t="s">
         <v>877</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="708" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A708" t="s">
         <v>877</v>
       </c>
@@ -15456,7 +15456,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="709" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A709" t="s">
         <v>877</v>
       </c>
@@ -15470,7 +15470,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="710" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A710" t="s">
         <v>877</v>
       </c>
@@ -15484,7 +15484,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A711" t="s">
         <v>877</v>
       </c>
@@ -15498,7 +15498,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="712" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A712" t="s">
         <v>877</v>
       </c>
@@ -15512,7 +15512,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="713" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A713" t="s">
         <v>877</v>
       </c>
@@ -15540,7 +15540,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="715" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A715" t="s">
         <v>877</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="716" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A716" t="s">
         <v>877</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="717" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A717" t="s">
         <v>877</v>
       </c>
@@ -15596,7 +15596,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="719" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A719" t="s">
         <v>877</v>
       </c>
@@ -15666,7 +15666,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="724" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A724" t="s">
         <v>877</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A725" t="s">
         <v>877</v>
       </c>
@@ -15694,7 +15694,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="726" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A726" t="s">
         <v>877</v>
       </c>
@@ -15722,7 +15722,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="728" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A728" t="s">
         <v>877</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="729" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A729" t="s">
         <v>877</v>
       </c>
@@ -15750,7 +15750,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="730" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A730" t="s">
         <v>877</v>
       </c>
@@ -15806,7 +15806,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="734" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A734" t="s">
         <v>877</v>
       </c>
@@ -15820,7 +15820,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="735" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A735" t="s">
         <v>877</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="736" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A736" t="s">
         <v>877</v>
       </c>
@@ -15904,7 +15904,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="741" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A741" t="s">
         <v>877</v>
       </c>
@@ -15932,7 +15932,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="743" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A743" t="s">
         <v>877</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="747" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A747" t="s">
         <v>877</v>
       </c>
@@ -16030,7 +16030,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="750" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A750" t="s">
         <v>877</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="751" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A751" t="s">
         <v>877</v>
       </c>
@@ -16058,7 +16058,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="752" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A752" t="s">
         <v>877</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="754" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A754" t="s">
         <v>877</v>
       </c>
@@ -16100,7 +16100,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="755" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A755" t="s">
         <v>877</v>
       </c>
@@ -16128,7 +16128,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="757" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A757" t="s">
         <v>877</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="762" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A762" t="s">
         <v>877</v>
       </c>
@@ -16226,7 +16226,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="764" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A764" t="s">
         <v>877</v>
       </c>
@@ -16254,7 +16254,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="766" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A766" t="s">
         <v>877</v>
       </c>
@@ -16282,7 +16282,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="768" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A768" t="s">
         <v>877</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="769" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A769" t="s">
         <v>877</v>
       </c>
@@ -16310,7 +16310,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="770" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A770" t="s">
         <v>877</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="771" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A771" t="s">
         <v>877</v>
       </c>
@@ -16338,7 +16338,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="772" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A772" t="s">
         <v>877</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="774" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A774" t="s">
         <v>877</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="776" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A776" t="s">
         <v>877</v>
       </c>
@@ -16478,7 +16478,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="782" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A782" t="s">
         <v>877</v>
       </c>
@@ -16492,7 +16492,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="783" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A783" t="s">
         <v>877</v>
       </c>
@@ -16506,7 +16506,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="784" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A784" t="s">
         <v>877</v>
       </c>
@@ -16534,7 +16534,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="786" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A786" t="s">
         <v>877</v>
       </c>
@@ -16576,7 +16576,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="789" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A789" t="s">
         <v>877</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="791" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A791" t="s">
         <v>877</v>
       </c>
@@ -16629,7 +16629,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="793" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A793" t="s">
         <v>877</v>
       </c>
@@ -16693,7 +16693,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="798" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A798" t="s">
         <v>877</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="799" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A799" t="s">
         <v>877</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="812" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A812" t="s">
         <v>877</v>
       </c>
@@ -16917,7 +16917,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="814" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A814" t="s">
         <v>877</v>
       </c>
@@ -16931,7 +16931,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="815" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A815" t="s">
         <v>877</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="816" spans="1:4" ht="57" hidden="1" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
       <c r="A816" t="s">
         <v>877</v>
       </c>
@@ -16973,7 +16973,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="818" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A818" t="s">
         <v>1365</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="819" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A819" t="s">
         <v>1365</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="820" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A820" t="s">
         <v>1365</v>
       </c>
@@ -17015,7 +17015,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="821" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A821" t="s">
         <v>1365</v>
       </c>
@@ -17057,7 +17057,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="824" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A824" t="s">
         <v>1365</v>
       </c>
@@ -17071,7 +17071,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="825" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A825" t="s">
         <v>1365</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="826" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A826" t="s">
         <v>1365</v>
       </c>
@@ -17127,7 +17127,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="829" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A829" t="s">
         <v>1365</v>
       </c>
@@ -17141,7 +17141,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="830" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A830" t="s">
         <v>1365</v>
       </c>
@@ -17183,7 +17183,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="833" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A833" t="s">
         <v>1365</v>
       </c>
@@ -17211,7 +17211,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="835" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A835" t="s">
         <v>1365</v>
       </c>
@@ -17225,7 +17225,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="836" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A836" t="s">
         <v>1365</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="837" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A837" t="s">
         <v>1365</v>
       </c>
@@ -17253,7 +17253,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="838" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="838" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A838" t="s">
         <v>1365</v>
       </c>
@@ -17267,7 +17267,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="839" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A839" t="s">
         <v>1365</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="840" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A840" t="s">
         <v>1365</v>
       </c>
@@ -17295,7 +17295,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="841" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A841" t="s">
         <v>1365</v>
       </c>
@@ -17351,7 +17351,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="845" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A845" t="s">
         <v>1365</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="847" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A847" t="s">
         <v>1365</v>
       </c>
@@ -17407,7 +17407,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="849" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A849" t="s">
         <v>1365</v>
       </c>
@@ -17463,7 +17463,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="853" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A853" t="s">
         <v>1365</v>
       </c>
@@ -17477,7 +17477,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="854" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A854" t="s">
         <v>1365</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="858" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A858" t="s">
         <v>1365</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="861" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>1365</v>
       </c>
@@ -17589,7 +17589,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="862" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>1365</v>
       </c>
@@ -17603,7 +17603,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="863" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A863" t="s">
         <v>1365</v>
       </c>
@@ -17645,7 +17645,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="866" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>1365</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="868" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>1365</v>
       </c>
@@ -17687,7 +17687,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="869" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>1365</v>
       </c>
@@ -17701,7 +17701,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="870" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>1365</v>
       </c>
@@ -17743,7 +17743,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="873" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A873" t="s">
         <v>1365</v>
       </c>
@@ -17757,7 +17757,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="874" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>1365</v>
       </c>
@@ -17771,7 +17771,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="875" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>1365</v>
       </c>
@@ -17813,7 +17813,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="878" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A878" t="s">
         <v>1365</v>
       </c>
@@ -17827,7 +17827,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="879" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A879" t="s">
         <v>1365</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="880" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A880" t="s">
         <v>1365</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="881" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A881" t="s">
         <v>1365</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="882" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A882" t="s">
         <v>1365</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="888" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A888" t="s">
         <v>1365</v>
       </c>
@@ -17981,7 +17981,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="890" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A890" t="s">
         <v>1365</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="892" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A892" t="s">
         <v>1365</v>
       </c>
@@ -18037,7 +18037,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="894" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A894" t="s">
         <v>1365</v>
       </c>
@@ -18051,7 +18051,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="895" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A895" t="s">
         <v>1365</v>
       </c>
@@ -18135,7 +18135,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="901" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="901" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A901" t="s">
         <v>1365</v>
       </c>
@@ -18149,7 +18149,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="902" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A902" t="s">
         <v>1365</v>
       </c>
@@ -18191,7 +18191,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="905" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="905" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A905" t="s">
         <v>1365</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="906" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A906" t="s">
         <v>1365</v>
       </c>
@@ -18219,7 +18219,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="907" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A907" t="s">
         <v>1365</v>
       </c>
@@ -18233,7 +18233,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="908" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="908" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A908" t="s">
         <v>1365</v>
       </c>
@@ -18275,7 +18275,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="911" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A911" t="s">
         <v>1365</v>
       </c>
@@ -18303,7 +18303,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="913" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A913" t="s">
         <v>1365</v>
       </c>
@@ -18401,7 +18401,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="920" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A920" t="s">
         <v>1365</v>
       </c>
@@ -18415,7 +18415,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="921" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A921" t="s">
         <v>1365</v>
       </c>
@@ -18443,7 +18443,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="923" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="923" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A923" t="s">
         <v>1365</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="926" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="926" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A926" t="s">
         <v>1365</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="927" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="927" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A927" t="s">
         <v>1365</v>
       </c>
@@ -18527,7 +18527,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="929" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="929" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A929" t="s">
         <v>1365</v>
       </c>
@@ -18555,7 +18555,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="931" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="931" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A931" t="s">
         <v>1365</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="938" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="938" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A938" t="s">
         <v>1365</v>
       </c>
@@ -18709,7 +18709,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="942" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="942" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A942" t="s">
         <v>1365</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="944" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="944" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A944" t="s">
         <v>1365</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="946" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="946" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A946" t="s">
         <v>1365</v>
       </c>
@@ -18779,7 +18779,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="947" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="947" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A947" t="s">
         <v>1365</v>
       </c>
@@ -18807,7 +18807,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="949" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="949" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A949" t="s">
         <v>1365</v>
       </c>
@@ -18821,7 +18821,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="950" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="950" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A950" t="s">
         <v>1365</v>
       </c>
@@ -18835,7 +18835,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="951" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="951" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A951" t="s">
         <v>1365</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="953" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="953" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A953" t="s">
         <v>1365</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="956" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="956" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A956" t="s">
         <v>1365</v>
       </c>
@@ -18927,7 +18927,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="958" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="958" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A958" t="s">
         <v>1365</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="960" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="960" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A960" t="s">
         <v>1365</v>
       </c>
@@ -18983,7 +18983,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="962" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="962" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A962" t="s">
         <v>1365</v>
       </c>
@@ -19011,7 +19011,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="964" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="964" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
       <c r="A964" t="s">
         <v>1365</v>
       </c>
@@ -19025,7 +19025,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="965" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="965" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A965" t="s">
         <v>1365</v>
       </c>
@@ -19039,7 +19039,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="966" spans="1:4" ht="42.75" hidden="1" x14ac:dyDescent="0.45">
+    <row r="966" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
       <c r="A966" t="s">
         <v>1365</v>
       </c>
@@ -19081,7 +19081,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="969" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="969" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A969" t="s">
         <v>1364</v>
       </c>
@@ -19095,7 +19095,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="970" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="970" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A970" t="s">
         <v>1364</v>
       </c>
@@ -19109,7 +19109,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="971" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="971" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A971" t="s">
         <v>1364</v>
       </c>
@@ -19123,7 +19123,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="972" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="972" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A972" t="s">
         <v>1364</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="973" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="973" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A973" t="s">
         <v>1364</v>
       </c>
@@ -19151,7 +19151,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="974" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="974" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A974" t="s">
         <v>1364</v>
       </c>
@@ -19165,7 +19165,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="975" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="975" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A975" t="s">
         <v>1364</v>
       </c>
@@ -19179,7 +19179,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="976" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="976" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A976" t="s">
         <v>1364</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="977" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="977" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A977" t="s">
         <v>1364</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="978" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="978" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A978" t="s">
         <v>1364</v>
       </c>
@@ -19221,7 +19221,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="979" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="979" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A979" t="s">
         <v>1364</v>
       </c>
@@ -19235,7 +19235,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="980" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="980" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A980" t="s">
         <v>1364</v>
       </c>
@@ -19249,7 +19249,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="981" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="981" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A981" t="s">
         <v>1364</v>
       </c>
@@ -19263,7 +19263,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="982" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="982" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A982" t="s">
         <v>1364</v>
       </c>
@@ -19277,7 +19277,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="983" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="983" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A983" t="s">
         <v>1364</v>
       </c>
@@ -19291,7 +19291,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="984" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="984" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A984" t="s">
         <v>1364</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="985" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="985" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A985" t="s">
         <v>1364</v>
       </c>
@@ -19319,7 +19319,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="986" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="986" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A986" t="s">
         <v>1364</v>
       </c>
@@ -19333,7 +19333,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="987" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="987" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A987" t="s">
         <v>1364</v>
       </c>
@@ -19347,7 +19347,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="988" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="988" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A988" t="s">
         <v>1364</v>
       </c>
@@ -19361,7 +19361,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="989" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="989" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A989" t="s">
         <v>1364</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="990" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="990" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A990" t="s">
         <v>1364</v>
       </c>
@@ -19389,7 +19389,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="991" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="991" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A991" t="s">
         <v>1364</v>
       </c>
@@ -19403,7 +19403,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="992" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="992" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A992" t="s">
         <v>1364</v>
       </c>
@@ -19417,7 +19417,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="993" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="993" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A993" t="s">
         <v>1364</v>
       </c>
@@ -19431,7 +19431,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="994" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="994" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A994" t="s">
         <v>1364</v>
       </c>
@@ -19445,7 +19445,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="995" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="995" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A995" t="s">
         <v>1364</v>
       </c>
@@ -19459,7 +19459,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="996" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="996" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A996" t="s">
         <v>1364</v>
       </c>
@@ -19473,7 +19473,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="997" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="997" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A997" t="s">
         <v>1364</v>
       </c>
@@ -19487,7 +19487,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="998" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="998" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A998" t="s">
         <v>1364</v>
       </c>
@@ -19501,7 +19501,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="999" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="999" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A999" t="s">
         <v>1364</v>
       </c>
@@ -19529,7 +19529,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="1001" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1001" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1001" t="s">
         <v>1364</v>
       </c>
@@ -19543,7 +19543,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="1002" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1002" t="s">
         <v>1364</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="1003" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1003" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1003" t="s">
         <v>1364</v>
       </c>
@@ -19571,7 +19571,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="1004" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1004" t="s">
         <v>1364</v>
       </c>
@@ -19585,7 +19585,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="1005" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1005" t="s">
         <v>1364</v>
       </c>
@@ -19613,7 +19613,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="1007" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1007" t="s">
         <v>1364</v>
       </c>
@@ -19627,7 +19627,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="1008" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1008" t="s">
         <v>1364</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="1009" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1009" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1009" t="s">
         <v>1364</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="1010" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1010" t="s">
         <v>1364</v>
       </c>
@@ -19669,7 +19669,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="1011" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1011" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1011" t="s">
         <v>1364</v>
       </c>
@@ -19683,7 +19683,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="1012" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1012" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1012" t="s">
         <v>1364</v>
       </c>
@@ -19697,7 +19697,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="1013" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1013" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1013" t="s">
         <v>1364</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="1014" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1014" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1014" t="s">
         <v>1364</v>
       </c>
@@ -19725,7 +19725,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="1015" spans="1:4" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1015" t="s">
         <v>1364</v>
       </c>
@@ -19739,7 +19739,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="1016" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1016" t="s">
         <v>1364</v>
       </c>
@@ -19753,7 +19753,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="1017" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1017" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1017" t="s">
         <v>1364</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="1018" spans="1:4" ht="28.5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="1018" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A1018" t="s">
         <v>1364</v>
       </c>
@@ -19783,87 +19783,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I1018" xr:uid="{1CE6CCED-2063-47D5-99CF-26463EA19C1D}">
-    <filterColumn colId="2">
+    <filterColumn colId="0">
       <filters>
-        <filter val="0, 10"/>
-        <filter val="0,10, 17"/>
-        <filter val="1, 10"/>
-        <filter val="1, 10, 11"/>
-        <filter val="1, 10, 11, 13"/>
-        <filter val="1, 10, 17"/>
-        <filter val="1, 10, 17, 16"/>
-        <filter val="1, 10, 7, 2"/>
-        <filter val="1, 10, 8"/>
-        <filter val="1, 17, 10"/>
-        <filter val="1, 2, 10"/>
-        <filter val="1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 16, 17"/>
-        <filter val="1, 3, 10"/>
-        <filter val="1, 3, 4, 10"/>
-        <filter val="1, 4, 10, 11"/>
-        <filter val="1, 5, 8, 10"/>
-        <filter val="1, 7, 11, 10"/>
-        <filter val="1, 8, 10"/>
-        <filter val="1, 8, 10, 13, 17"/>
-        <filter val="10"/>
-        <filter val="10, 0"/>
-        <filter val="10, 1"/>
-        <filter val="10, 1, 9"/>
-        <filter val="10, 11"/>
-        <filter val="10, 16"/>
-        <filter val="10, 16, 17"/>
-        <filter val="10, 17"/>
-        <filter val="10, 17, 0"/>
-        <filter val="10, 17, 13"/>
-        <filter val="10, 2"/>
-        <filter val="10, 3"/>
-        <filter val="10, 5"/>
-        <filter val="10, 8, 17"/>
-        <filter val="11, 10"/>
-        <filter val="11, 10, 16"/>
-        <filter val="12, 10"/>
-        <filter val="13, 10, 17"/>
-        <filter val="13, 11, 10"/>
-        <filter val="13, 12, 8, 10, 16, 17"/>
-        <filter val="13, 7, 10"/>
-        <filter val="15, 10, 12"/>
-        <filter val="16, 10"/>
-        <filter val="16, 10, 4"/>
-        <filter val="16, 4, 10"/>
-        <filter val="16, 5, 10"/>
-        <filter val="17, 10"/>
-        <filter val="17, 10, 1"/>
-        <filter val="17, 10, 13, 8"/>
-        <filter val="17, 10, 8"/>
-        <filter val="17, 13, 10"/>
-        <filter val="17, 16, 10"/>
-        <filter val="17, 7, 13, 10"/>
-        <filter val="17, 9, 10"/>
-        <filter val="2, 1, 10"/>
-        <filter val="2, 10"/>
-        <filter val="2, 12, 10"/>
-        <filter val="2, 5, 10"/>
-        <filter val="3, 1, 10"/>
-        <filter val="3, 10"/>
-        <filter val="3, 10, 16"/>
-        <filter val="3, 4, 6, 11, 10, 1, 13"/>
-        <filter val="3, 5, 10"/>
-        <filter val="3, 5. 10"/>
-        <filter val="4, 10"/>
-        <filter val="4, 10, 1"/>
-        <filter val="4, 10, 16"/>
-        <filter val="4, 5, 10"/>
-        <filter val="4, 8, 5,9, 10"/>
-        <filter val="4, 9, 10"/>
-        <filter val="5, 10"/>
-        <filter val="5, 10, 4"/>
-        <filter val="7, 10"/>
-        <filter val="7, 8, 10, 13"/>
-        <filter val="7, 8, 9, 10, 11"/>
-        <filter val="8, 10"/>
-        <filter val="8, 10, 13"/>
-        <filter val="9, 10"/>
-        <filter val="9, 10, 17"/>
-        <filter val="9, 5, 13, 10"/>
+        <filter val="G20_2024_"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19875,7 +19797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4C1530-F061-4D76-89DF-324CB83EC928}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="6"/>
@@ -20108,7 +20030,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="31.5" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>15</v>
       </c>
@@ -20122,7 +20044,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="61.9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="61.9" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>16</v>
       </c>
@@ -20136,7 +20058,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="41.65" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="41.65" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>17</v>
       </c>
@@ -20150,141 +20072,138 @@
         <v>266</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C26" s="16" t="s">
+    <row r="20" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-    </row>
-    <row r="27" spans="1:8" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="C27" s="8">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" spans="1:6" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A22" s="8">
         <v>0</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E27" s="7">
+      <c r="C22" s="7">
         <v>6</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="7">
+      <c r="E22" s="7">
         <v>12</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="F22" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="C28" s="8">
+    <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="8">
         <v>1</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="7">
+      <c r="C23" s="7">
         <v>7</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="7">
+      <c r="E23" s="7">
         <v>13</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="C29" s="8">
+    <row r="24" spans="1:6" ht="27.75" x14ac:dyDescent="0.45">
+      <c r="A24" s="8">
         <v>2</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="B24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="7">
+      <c r="C24" s="7">
         <v>8</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="7">
+      <c r="E24" s="7">
         <v>14</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="F24" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="54.75" x14ac:dyDescent="0.45">
-      <c r="C30" s="8">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="8">
         <v>3</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="7">
+      <c r="C25" s="7">
         <v>9</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G30" s="7">
+      <c r="E25" s="7">
         <v>15</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="57" x14ac:dyDescent="0.45">
-      <c r="C31" s="8">
+    <row r="26" spans="1:6" ht="57" x14ac:dyDescent="0.45">
+      <c r="A26" s="8">
         <v>4</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="B26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="7">
+      <c r="C26" s="7">
         <v>10</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="7">
+      <c r="E26" s="7">
         <v>16</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="F26" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="71.650000000000006" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C32" s="11">
+    <row r="27" spans="1:6" ht="71.650000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="11">
         <v>5</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="B27" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E32" s="13">
+      <c r="C27" s="13">
         <v>11</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="D27" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="13">
+      <c r="E27" s="13">
         <v>17</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="F27" s="14" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C26:H26"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>